--- a/Listes LOUMAS phases1&2.xlsx
+++ b/Listes LOUMAS phases1&2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="183">
   <si>
     <t>DRV</t>
   </si>
@@ -553,34 +553,46 @@
     <t>SUD</t>
   </si>
   <si>
-    <t>DJIBANAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 12.543907,-15810159</t>
-  </si>
-  <si>
-    <t>DIAOBE</t>
-  </si>
-  <si>
-    <t>12.915496 ,-14.150688</t>
-  </si>
-  <si>
-    <t>BAYENGOU</t>
-  </si>
-  <si>
     <t>13.207572, -15.145006</t>
   </si>
   <si>
-    <t>MANDA DOUANE</t>
-  </si>
-  <si>
-    <t>13.3339667,-13.8229600</t>
-  </si>
-  <si>
-    <t>SARE YOBA</t>
-  </si>
-  <si>
-    <t>12.76538, -15.105637</t>
+    <t>TEMENTO</t>
+  </si>
+  <si>
+    <t>12.79213;-13.83465</t>
+  </si>
+  <si>
+    <t>PATA</t>
+  </si>
+  <si>
+    <t>CARREFOUR NDIAYE</t>
+  </si>
+  <si>
+    <t>12.5448.4N-153505.8W</t>
+  </si>
+  <si>
+    <t>NDIAMACOUTA</t>
+  </si>
+  <si>
+    <t>13.312147-15.635571</t>
+  </si>
+  <si>
+    <t>Mercredi</t>
+  </si>
+  <si>
+    <t>SARE ALKALY</t>
+  </si>
+  <si>
+    <t>13.249037-15.527020</t>
+  </si>
+  <si>
+    <t>jeudi</t>
+  </si>
+  <si>
+    <t>12.2829.8N-15.4444.5W</t>
+  </si>
+  <si>
+    <t>Vendredi</t>
   </si>
 </sst>
 </file>
@@ -646,7 +658,7 @@
       <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -671,6 +683,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="32">
     <border>
@@ -1075,7 +1093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1095,54 +1113,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1157,42 +1127,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1202,7 +1142,100 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1488,7 +1521,7 @@
   <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="25"/>
+    <col min="1" max="1" width="10.90625" style="9"/>
     <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.26953125" bestFit="1" customWidth="1"/>
@@ -1500,53 +1533,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="18"/>
-      <c r="H1" s="9" t="s">
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="H1" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
     </row>
     <row r="2" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
     </row>
     <row r="3" spans="2:12" ht="15" customHeight="1" thickBot="1">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="24"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="2:12" ht="28.5" thickBot="1">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="13" t="s">
         <v>3</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -1566,46 +1599,46 @@
       </c>
     </row>
     <row r="5" spans="2:12">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="K5" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="L5" s="38" t="s">
+      <c r="L5" s="17" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="B6" s="16"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="H6" s="39"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="6" t="s">
         <v>99</v>
       </c>
@@ -1615,22 +1648,22 @@
       <c r="K6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="L6" s="40" t="s">
+      <c r="L6" s="18" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="16"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="39"/>
+      <c r="H7" s="27"/>
       <c r="I7" s="6" t="s">
         <v>102</v>
       </c>
@@ -1640,22 +1673,22 @@
       <c r="K7" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="L7" s="40" t="s">
+      <c r="L7" s="18" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="16"/>
+      <c r="B8" s="36"/>
       <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="39"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="6" t="s">
         <v>105</v>
       </c>
@@ -1665,22 +1698,22 @@
       <c r="K8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="40" t="s">
+      <c r="L8" s="18" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="16"/>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="36"/>
+      <c r="C9" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="49" t="s">
+      <c r="E9" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="39"/>
+      <c r="H9" s="27"/>
       <c r="I9" s="6" t="s">
         <v>107</v>
       </c>
@@ -1690,76 +1723,76 @@
       <c r="K9" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="L9" s="40" t="s">
+      <c r="L9" s="18" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1">
-      <c r="B10" s="31"/>
-      <c r="C10" s="32" t="s">
+      <c r="B10" s="37"/>
+      <c r="C10" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="41"/>
-      <c r="I10" s="42" t="s">
+      <c r="H10" s="28"/>
+      <c r="I10" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J10" s="42" t="s">
+      <c r="J10" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="K10" s="42" t="s">
+      <c r="K10" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="43" t="s">
+      <c r="L10" s="20" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="11" spans="2:12">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="L11" s="38" t="s">
+      <c r="L11" s="17" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="12" spans="2:12">
-      <c r="B12" s="16"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="5" t="s">
         <v>151</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="45"/>
+      <c r="H12" s="50"/>
       <c r="I12" s="6" t="s">
         <v>134</v>
       </c>
@@ -1769,22 +1802,22 @@
       <c r="K12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="L12" s="40" t="s">
+      <c r="L12" s="18" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="16"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="5" t="s">
         <v>152</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="48" t="s">
+      <c r="E13" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="H13" s="45"/>
+      <c r="H13" s="50"/>
       <c r="I13" s="6" t="s">
         <v>137</v>
       </c>
@@ -1794,22 +1827,22 @@
       <c r="K13" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="L13" s="40" t="s">
+      <c r="L13" s="18" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="16"/>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="36"/>
+      <c r="C14" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="55" t="s">
         <v>161</v>
       </c>
-      <c r="H14" s="45"/>
+      <c r="H14" s="50"/>
       <c r="I14" s="6" t="s">
         <v>140</v>
       </c>
@@ -1819,22 +1852,22 @@
       <c r="K14" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="L14" s="40" t="s">
+      <c r="L14" s="18" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="16"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="8" t="s">
         <v>154</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="45"/>
+      <c r="H15" s="50"/>
       <c r="I15" s="6" t="s">
         <v>143</v>
       </c>
@@ -1844,76 +1877,76 @@
       <c r="K15" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L15" s="40" t="s">
+      <c r="L15" s="18" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="15" thickBot="1">
-      <c r="B16" s="31"/>
-      <c r="C16" s="32" t="s">
+      <c r="B16" s="37"/>
+      <c r="C16" s="58" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="42" t="s">
+      <c r="H16" s="51"/>
+      <c r="I16" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="J16" s="42" t="s">
+      <c r="J16" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="K16" s="42" t="s">
+      <c r="K16" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="L16" s="43" t="s">
+      <c r="L16" s="20" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="17" spans="2:12">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E17" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="36" t="s">
+      <c r="H17" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="37" t="s">
+      <c r="I17" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="37" t="s">
+      <c r="J17" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="K17" s="37" t="s">
+      <c r="K17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L17" s="38" t="s">
+      <c r="L17" s="17" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="2:12">
-      <c r="B18" s="34"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="48" t="s">
+      <c r="E18" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="39"/>
+      <c r="H18" s="27"/>
       <c r="I18" s="6" t="s">
         <v>59</v>
       </c>
@@ -1923,22 +1956,22 @@
       <c r="K18" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="40" t="s">
+      <c r="L18" s="18" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="34"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="48" t="s">
+      <c r="E19" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="39"/>
+      <c r="H19" s="27"/>
       <c r="I19" s="6" t="s">
         <v>63</v>
       </c>
@@ -1948,22 +1981,22 @@
       <c r="K19" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L19" s="40" t="s">
+      <c r="L19" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="20" spans="2:12">
-      <c r="B20" s="34"/>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="39"/>
+      <c r="C20" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="H20" s="27"/>
       <c r="I20" s="6" t="s">
         <v>67</v>
       </c>
@@ -1973,22 +2006,22 @@
       <c r="K20" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="L20" s="40" t="s">
+      <c r="L20" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="21" spans="2:12">
-      <c r="B21" s="34"/>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="39"/>
+      <c r="C21" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="39"/>
+      <c r="H21" s="27"/>
       <c r="I21" s="6" t="s">
         <v>70</v>
       </c>
@@ -1998,76 +2031,76 @@
       <c r="K21" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="L21" s="40" t="s">
+      <c r="L21" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="15" thickBot="1">
-      <c r="B22" s="35"/>
-      <c r="C22" s="32" t="s">
+      <c r="B22" s="40"/>
+      <c r="C22" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="H22" s="41"/>
-      <c r="I22" s="42" t="s">
+      <c r="H22" s="28"/>
+      <c r="I22" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="J22" s="42" t="s">
+      <c r="J22" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="K22" s="42" t="s">
+      <c r="K22" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="L22" s="43" t="s">
+      <c r="L22" s="20" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="36" t="s">
+      <c r="H23" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="I23" s="37" t="s">
+      <c r="I23" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="J23" s="37" t="s">
+      <c r="J23" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="K23" s="37" t="s">
+      <c r="K23" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="L23" s="38" t="s">
+      <c r="L23" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="24" spans="2:12">
-      <c r="B24" s="34"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="39"/>
+      <c r="H24" s="27"/>
       <c r="I24" s="6" t="s">
         <v>79</v>
       </c>
@@ -2077,22 +2110,22 @@
       <c r="K24" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="L24" s="40" t="s">
+      <c r="L24" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" spans="2:12">
-      <c r="B25" s="34"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="48" t="s">
+      <c r="E25" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="H25" s="39"/>
+      <c r="H25" s="27"/>
       <c r="I25" s="6" t="s">
         <v>82</v>
       </c>
@@ -2102,22 +2135,22 @@
       <c r="K25" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="L25" s="40" t="s">
+      <c r="L25" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="26" spans="2:12">
-      <c r="B26" s="34"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="48" t="s">
+      <c r="E26" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="H26" s="39"/>
+      <c r="H26" s="27"/>
       <c r="I26" s="6" t="s">
         <v>85</v>
       </c>
@@ -2127,22 +2160,22 @@
       <c r="K26" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="L26" s="40" t="s">
+      <c r="L26" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="27" spans="2:12">
-      <c r="B27" s="34"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="49" t="s">
+      <c r="E27" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="H27" s="39"/>
+      <c r="H27" s="27"/>
       <c r="I27" s="6" t="s">
         <v>88</v>
       </c>
@@ -2152,72 +2185,76 @@
       <c r="K27" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="L27" s="40" t="s">
+      <c r="L27" s="18" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="15" thickBot="1">
-      <c r="B28" s="35"/>
-      <c r="C28" s="32" t="s">
+      <c r="B28" s="40"/>
+      <c r="C28" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="E28" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="H28" s="41"/>
-      <c r="I28" s="42" t="s">
+      <c r="H28" s="28"/>
+      <c r="I28" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="J28" s="42" t="s">
+      <c r="J28" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="K28" s="42" t="s">
+      <c r="K28" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="L28" s="43" t="s">
+      <c r="L28" s="20" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="29" spans="2:12">
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30" t="s">
+      <c r="C29" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="H29" s="36" t="s">
+      <c r="E29" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="H29" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="I29" s="37" t="s">
+      <c r="I29" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="J29" s="37" t="s">
+      <c r="J29" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="K29" s="37" t="s">
+      <c r="K29" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L29" s="38" t="s">
+      <c r="L29" s="17" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="30" spans="2:12">
-      <c r="B30" s="34"/>
-      <c r="C30" s="5" t="s">
+      <c r="B30" s="39"/>
+      <c r="C30" s="54" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="55" t="s">
         <v>169</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" s="48" t="s">
-        <v>170</v>
-      </c>
-      <c r="H30" s="39"/>
+      <c r="H30" s="27"/>
       <c r="I30" s="6" t="s">
         <v>117</v>
       </c>
@@ -2227,22 +2264,22 @@
       <c r="K30" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="L30" s="40" t="s">
+      <c r="L30" s="18" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="31" spans="2:12">
-      <c r="B31" s="34"/>
-      <c r="C31" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="H31" s="39"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="54" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" s="27"/>
       <c r="I31" s="6" t="s">
         <v>120</v>
       </c>
@@ -2252,22 +2289,22 @@
       <c r="K31" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="L31" s="40" t="s">
+      <c r="L31" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="32" spans="2:12">
-      <c r="B32" s="34"/>
-      <c r="C32" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E32" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="H32" s="39"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" s="27"/>
       <c r="I32" s="6" t="s">
         <v>122</v>
       </c>
@@ -2277,22 +2314,22 @@
       <c r="K32" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="L32" s="40" t="s">
+      <c r="L32" s="18" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="33" spans="2:12">
-      <c r="B33" s="34"/>
-      <c r="C33" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="H33" s="39"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="D33" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="E33" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H33" s="27"/>
       <c r="I33" s="6" t="s">
         <v>125</v>
       </c>
@@ -2302,32 +2339,32 @@
       <c r="K33" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="L33" s="40" t="s">
+      <c r="L33" s="18" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="34" spans="2:12" ht="15" thickBot="1">
-      <c r="B34" s="35"/>
-      <c r="C34" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="51" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="41"/>
-      <c r="I34" s="42" t="s">
+      <c r="B34" s="40"/>
+      <c r="C34" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="J34" s="42" t="s">
+      <c r="D34" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="E34" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="H34" s="28"/>
+      <c r="I34" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="J34" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="K34" s="42" t="s">
+      <c r="K34" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="L34" s="43" t="s">
+      <c r="L34" s="20" t="s">
         <v>130</v>
       </c>
     </row>

--- a/Listes LOUMAS phases1&2.xlsx
+++ b/Listes LOUMAS phases1&2.xlsx
@@ -1142,84 +1142,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1237,6 +1159,84 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1533,41 +1533,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="42"/>
-      <c r="H1" s="29" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
+      <c r="H1" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
     </row>
     <row r="2" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B2" s="43"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
     </row>
     <row r="3" spans="2:12" ht="15" customHeight="1" thickBot="1">
-      <c r="B3" s="46"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="48"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
     </row>
     <row r="4" spans="2:12" ht="28.5" thickBot="1">
       <c r="B4" s="10" t="s">
@@ -1599,7 +1599,7 @@
       </c>
     </row>
     <row r="5" spans="2:12">
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="45" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -1611,7 +1611,7 @@
       <c r="E5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="36" t="s">
         <v>95</v>
       </c>
       <c r="I5" s="16" t="s">
@@ -1628,7 +1628,7 @@
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="B6" s="36"/>
+      <c r="B6" s="46"/>
       <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1638,7 +1638,7 @@
       <c r="E6" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="H6" s="27"/>
+      <c r="H6" s="37"/>
       <c r="I6" s="6" t="s">
         <v>99</v>
       </c>
@@ -1653,7 +1653,7 @@
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="36"/>
+      <c r="B7" s="46"/>
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
@@ -1663,7 +1663,7 @@
       <c r="E7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="27"/>
+      <c r="H7" s="37"/>
       <c r="I7" s="6" t="s">
         <v>102</v>
       </c>
@@ -1678,7 +1678,7 @@
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="36"/>
+      <c r="B8" s="46"/>
       <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
@@ -1688,7 +1688,7 @@
       <c r="E8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="27"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="6" t="s">
         <v>105</v>
       </c>
@@ -1703,17 +1703,17 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="36"/>
-      <c r="C9" s="56" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="27"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="6" t="s">
         <v>107</v>
       </c>
@@ -1728,7 +1728,7 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1">
-      <c r="B10" s="37"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="15" t="s">
         <v>18</v>
       </c>
@@ -1738,7 +1738,7 @@
       <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="38"/>
       <c r="I10" s="19" t="s">
         <v>110</v>
       </c>
@@ -1753,7 +1753,7 @@
       </c>
     </row>
     <row r="11" spans="2:12">
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="45" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1765,7 +1765,7 @@
       <c r="E11" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="49" t="s">
+      <c r="H11" s="59" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="16" t="s">
@@ -1782,7 +1782,7 @@
       </c>
     </row>
     <row r="12" spans="2:12">
-      <c r="B12" s="36"/>
+      <c r="B12" s="46"/>
       <c r="C12" s="5" t="s">
         <v>151</v>
       </c>
@@ -1792,7 +1792,7 @@
       <c r="E12" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="50"/>
+      <c r="H12" s="60"/>
       <c r="I12" s="6" t="s">
         <v>134</v>
       </c>
@@ -1807,7 +1807,7 @@
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="36"/>
+      <c r="B13" s="46"/>
       <c r="C13" s="5" t="s">
         <v>152</v>
       </c>
@@ -1817,7 +1817,7 @@
       <c r="E13" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="H13" s="50"/>
+      <c r="H13" s="60"/>
       <c r="I13" s="6" t="s">
         <v>137</v>
       </c>
@@ -1832,17 +1832,17 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="36"/>
-      <c r="C14" s="54" t="s">
+      <c r="B14" s="46"/>
+      <c r="C14" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="55" t="s">
+      <c r="E14" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="H14" s="50"/>
+      <c r="H14" s="60"/>
       <c r="I14" s="6" t="s">
         <v>140</v>
       </c>
@@ -1857,7 +1857,7 @@
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="36"/>
+      <c r="B15" s="46"/>
       <c r="C15" s="8" t="s">
         <v>154</v>
       </c>
@@ -1867,7 +1867,7 @@
       <c r="E15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="50"/>
+      <c r="H15" s="60"/>
       <c r="I15" s="6" t="s">
         <v>143</v>
       </c>
@@ -1882,17 +1882,17 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="15" thickBot="1">
-      <c r="B16" s="37"/>
-      <c r="C16" s="58" t="s">
+      <c r="B16" s="47"/>
+      <c r="C16" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="60" t="s">
+      <c r="E16" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="H16" s="51"/>
+      <c r="H16" s="61"/>
       <c r="I16" s="19" t="s">
         <v>146</v>
       </c>
@@ -1907,7 +1907,7 @@
       </c>
     </row>
     <row r="17" spans="2:12">
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="48" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="14" t="s">
@@ -1919,7 +1919,7 @@
       <c r="E17" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="26" t="s">
+      <c r="H17" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I17" s="16" t="s">
@@ -1936,7 +1936,7 @@
       </c>
     </row>
     <row r="18" spans="2:12">
-      <c r="B18" s="39"/>
+      <c r="B18" s="49"/>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
@@ -1946,7 +1946,7 @@
       <c r="E18" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="27"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="6" t="s">
         <v>59</v>
       </c>
@@ -1961,7 +1961,7 @@
       </c>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="39"/>
+      <c r="B19" s="49"/>
       <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
@@ -1971,7 +1971,7 @@
       <c r="E19" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="27"/>
+      <c r="H19" s="37"/>
       <c r="I19" s="6" t="s">
         <v>63</v>
       </c>
@@ -1986,17 +1986,17 @@
       </c>
     </row>
     <row r="20" spans="2:12">
-      <c r="B20" s="39"/>
-      <c r="C20" s="54" t="s">
+      <c r="B20" s="49"/>
+      <c r="C20" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="54" t="s">
+      <c r="D20" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="61" t="s">
+      <c r="E20" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="27"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="6" t="s">
         <v>67</v>
       </c>
@@ -2011,17 +2011,17 @@
       </c>
     </row>
     <row r="21" spans="2:12">
-      <c r="B21" s="39"/>
-      <c r="C21" s="56" t="s">
+      <c r="B21" s="49"/>
+      <c r="C21" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="56" t="s">
+      <c r="D21" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="55" t="s">
+      <c r="E21" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="27"/>
+      <c r="H21" s="37"/>
       <c r="I21" s="6" t="s">
         <v>70</v>
       </c>
@@ -2036,17 +2036,17 @@
       </c>
     </row>
     <row r="22" spans="2:12" ht="15" thickBot="1">
-      <c r="B22" s="40"/>
-      <c r="C22" s="58" t="s">
+      <c r="B22" s="50"/>
+      <c r="C22" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="58" t="s">
+      <c r="D22" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="H22" s="28"/>
+      <c r="H22" s="38"/>
       <c r="I22" s="19" t="s">
         <v>73</v>
       </c>
@@ -2061,7 +2061,7 @@
       </c>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="48" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="14" t="s">
@@ -2073,7 +2073,7 @@
       <c r="E23" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="26" t="s">
+      <c r="H23" s="36" t="s">
         <v>40</v>
       </c>
       <c r="I23" s="16" t="s">
@@ -2090,7 +2090,7 @@
       </c>
     </row>
     <row r="24" spans="2:12">
-      <c r="B24" s="39"/>
+      <c r="B24" s="49"/>
       <c r="C24" s="5" t="s">
         <v>43</v>
       </c>
@@ -2100,7 +2100,7 @@
       <c r="E24" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="27"/>
+      <c r="H24" s="37"/>
       <c r="I24" s="6" t="s">
         <v>79</v>
       </c>
@@ -2115,7 +2115,7 @@
       </c>
     </row>
     <row r="25" spans="2:12">
-      <c r="B25" s="39"/>
+      <c r="B25" s="49"/>
       <c r="C25" s="5" t="s">
         <v>45</v>
       </c>
@@ -2125,7 +2125,7 @@
       <c r="E25" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="H25" s="27"/>
+      <c r="H25" s="37"/>
       <c r="I25" s="6" t="s">
         <v>82</v>
       </c>
@@ -2140,7 +2140,7 @@
       </c>
     </row>
     <row r="26" spans="2:12">
-      <c r="B26" s="39"/>
+      <c r="B26" s="49"/>
       <c r="C26" s="5" t="s">
         <v>46</v>
       </c>
@@ -2150,7 +2150,7 @@
       <c r="E26" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="H26" s="27"/>
+      <c r="H26" s="37"/>
       <c r="I26" s="6" t="s">
         <v>85</v>
       </c>
@@ -2165,7 +2165,7 @@
       </c>
     </row>
     <row r="27" spans="2:12">
-      <c r="B27" s="39"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="8" t="s">
         <v>47</v>
       </c>
@@ -2175,7 +2175,7 @@
       <c r="E27" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="H27" s="27"/>
+      <c r="H27" s="37"/>
       <c r="I27" s="6" t="s">
         <v>88</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
     </row>
     <row r="28" spans="2:12" ht="15" thickBot="1">
-      <c r="B28" s="40"/>
+      <c r="B28" s="50"/>
       <c r="C28" s="15" t="s">
         <v>48</v>
       </c>
@@ -2200,7 +2200,7 @@
       <c r="E28" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="H28" s="28"/>
+      <c r="H28" s="38"/>
       <c r="I28" s="19" t="s">
         <v>92</v>
       </c>
@@ -2215,19 +2215,19 @@
       </c>
     </row>
     <row r="29" spans="2:12">
-      <c r="B29" s="38" t="s">
+      <c r="B29" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D29" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="53" t="s">
+      <c r="E29" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="H29" s="26" t="s">
+      <c r="H29" s="36" t="s">
         <v>113</v>
       </c>
       <c r="I29" s="16" t="s">
@@ -2244,17 +2244,17 @@
       </c>
     </row>
     <row r="30" spans="2:12">
-      <c r="B30" s="39"/>
-      <c r="C30" s="54" t="s">
+      <c r="B30" s="49"/>
+      <c r="C30" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D30" s="54" t="s">
+      <c r="D30" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="E30" s="55" t="s">
+      <c r="E30" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="H30" s="27"/>
+      <c r="H30" s="37"/>
       <c r="I30" s="6" t="s">
         <v>117</v>
       </c>
@@ -2269,17 +2269,17 @@
       </c>
     </row>
     <row r="31" spans="2:12">
-      <c r="B31" s="39"/>
-      <c r="C31" s="54" t="s">
+      <c r="B31" s="49"/>
+      <c r="C31" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="D31" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="55" t="s">
+      <c r="E31" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="H31" s="27"/>
+      <c r="H31" s="37"/>
       <c r="I31" s="6" t="s">
         <v>120</v>
       </c>
@@ -2294,17 +2294,17 @@
       </c>
     </row>
     <row r="32" spans="2:12">
-      <c r="B32" s="39"/>
-      <c r="C32" s="54" t="s">
+      <c r="B32" s="49"/>
+      <c r="C32" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="D32" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="E32" s="55" t="s">
+      <c r="E32" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="H32" s="27"/>
+      <c r="H32" s="37"/>
       <c r="I32" s="6" t="s">
         <v>122</v>
       </c>
@@ -2319,17 +2319,17 @@
       </c>
     </row>
     <row r="33" spans="2:12">
-      <c r="B33" s="39"/>
-      <c r="C33" s="56" t="s">
+      <c r="B33" s="49"/>
+      <c r="C33" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="D33" s="56" t="s">
+      <c r="D33" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="H33" s="27"/>
+      <c r="H33" s="37"/>
       <c r="I33" s="6" t="s">
         <v>125</v>
       </c>
@@ -2344,17 +2344,17 @@
       </c>
     </row>
     <row r="34" spans="2:12" ht="15" thickBot="1">
-      <c r="B34" s="40"/>
-      <c r="C34" s="58" t="s">
+      <c r="B34" s="50"/>
+      <c r="C34" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="58" t="s">
+      <c r="D34" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="E34" s="59" t="s">
+      <c r="E34" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="H34" s="28"/>
+      <c r="H34" s="38"/>
       <c r="I34" s="19" t="s">
         <v>128</v>
       </c>

--- a/Listes LOUMAS phases1&2.xlsx
+++ b/Listes LOUMAS phases1&2.xlsx
@@ -9,10 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="7050" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="List Phase1&amp;2" sheetId="1" r:id="rId1"/>
+    <sheet name="List Phase1&amp;2 maj" sheetId="4" r:id="rId2"/>
+    <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="207">
   <si>
     <t>DRV</t>
   </si>
@@ -216,9 +218,6 @@
   </si>
   <si>
     <t>BIRKILANE</t>
-  </si>
-  <si>
-    <t>14.12678°N; 15.73993°O</t>
   </si>
   <si>
     <t>DIMANCHE</t>
@@ -594,12 +593,87 @@
   <si>
     <t>Vendredi</t>
   </si>
+  <si>
+    <t>JOUR</t>
+  </si>
+  <si>
+    <t>NDIENE LAGUANE</t>
+  </si>
+  <si>
+    <t>14.512415,-15.924362</t>
+  </si>
+  <si>
+    <t>13.878041,-16.374332</t>
+  </si>
+  <si>
+    <t>DIAKHAO</t>
+  </si>
+  <si>
+    <t>14.463398,-16.286104</t>
+  </si>
+  <si>
+    <t>DAY OFF</t>
+  </si>
+  <si>
+    <t>PASSY</t>
+  </si>
+  <si>
+    <t>13.986325,-16.258516</t>
+  </si>
+  <si>
+    <t>NGOYE (Axe Loul Sessene)</t>
+  </si>
+  <si>
+    <t>14.355134,-16.629496</t>
+  </si>
+  <si>
+    <t>NGUENIENE</t>
+  </si>
+  <si>
+    <t>MBAFAYE</t>
+  </si>
+  <si>
+    <t>14.538246,-16.726216</t>
+  </si>
+  <si>
+    <t>14.426406, -16.40464</t>
+  </si>
+  <si>
+    <t>NDIOTE SEANE</t>
+  </si>
+  <si>
+    <t>TOUBA MOURID</t>
+  </si>
+  <si>
+    <t>13.8015460- 16.3271591</t>
+  </si>
+  <si>
+    <t>BOUNKILING</t>
+  </si>
+  <si>
+    <t>13.0402515, -15,6943034</t>
+  </si>
+  <si>
+    <t>DRSE</t>
+  </si>
+  <si>
+    <t>DRC</t>
+  </si>
+  <si>
+    <t>DRE</t>
+  </si>
+  <si>
+    <t>DRN</t>
+  </si>
+  <si>
+    <t>DRS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,8 +731,27 @@
       <color rgb="FF000000"/>
       <name val="Aptos"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF212121"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,8 +782,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="32">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1089,11 +1188,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1238,6 +1363,67 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1540,7 +1726,7 @@
       <c r="D1" s="51"/>
       <c r="E1" s="52"/>
       <c r="H1" s="39" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I1" s="40"/>
       <c r="J1" s="40"/>
@@ -1606,25 +1792,25 @@
         <v>5</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>6</v>
       </c>
       <c r="H5" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="J5" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="K5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="17" t="s">
         <v>97</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -1636,20 +1822,20 @@
         <v>8</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H6" s="37"/>
       <c r="I6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="K6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="7" spans="2:12">
@@ -1665,16 +1851,16 @@
       </c>
       <c r="H7" s="37"/>
       <c r="I7" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="K7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="18" t="s">
         <v>103</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -1690,16 +1876,16 @@
       </c>
       <c r="H8" s="37"/>
       <c r="I8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>57</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="2:12">
@@ -1715,16 +1901,16 @@
       </c>
       <c r="H9" s="37"/>
       <c r="I9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="K9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1">
@@ -1740,16 +1926,16 @@
       </c>
       <c r="H10" s="38"/>
       <c r="I10" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="J10" s="19" t="s">
         <v>110</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>111</v>
       </c>
       <c r="K10" s="19" t="s">
         <v>61</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="2:12">
@@ -1757,34 +1943,35 @@
         <v>21</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>167</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="G11" s="9"/>
       <c r="H11" s="59" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="J11" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="K11" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="17" t="s">
         <v>132</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="12" spans="2:12">
       <c r="B12" s="46"/>
       <c r="C12" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>23</v>
@@ -1792,74 +1979,75 @@
       <c r="E12" s="22" t="s">
         <v>24</v>
       </c>
+      <c r="G12" s="9"/>
       <c r="H12" s="60"/>
       <c r="I12" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="K12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" s="18" t="s">
         <v>135</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="L12" s="18" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="13" spans="2:12">
       <c r="B13" s="46"/>
       <c r="C13" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H13" s="60"/>
       <c r="I13" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="K13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="18" t="s">
         <v>138</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="14" spans="2:12">
       <c r="B14" s="46"/>
       <c r="C14" s="28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" s="28" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H14" s="60"/>
       <c r="I14" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>57</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="2:12">
       <c r="B15" s="46"/>
       <c r="C15" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>27</v>
@@ -1869,41 +2057,41 @@
       </c>
       <c r="H15" s="60"/>
       <c r="I15" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>61</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="15" thickBot="1">
       <c r="B16" s="47"/>
       <c r="C16" s="32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H16" s="61"/>
       <c r="I16" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="K16" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="20" t="s">
         <v>147</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="L16" s="20" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -1975,15 +2163,11 @@
       <c r="I19" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="6"/>
+      <c r="K19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="L19" s="18" t="s">
-        <v>66</v>
-      </c>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" spans="2:12">
       <c r="B20" s="49"/>
@@ -1994,20 +2178,20 @@
         <v>26</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H20" s="37"/>
       <c r="I20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="K20" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="L20" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -2019,17 +2203,17 @@
         <v>27</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H21" s="37"/>
       <c r="I21" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="K21" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="L21" s="18" t="s">
         <v>58</v>
@@ -2044,17 +2228,17 @@
         <v>29</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H22" s="38"/>
       <c r="I22" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="J22" s="19" t="s">
+      <c r="K22" s="19" t="s">
         <v>74</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>75</v>
       </c>
       <c r="L22" s="20" t="s">
         <v>62</v>
@@ -2077,16 +2261,16 @@
         <v>40</v>
       </c>
       <c r="I23" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="K23" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L23" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="L23" s="17" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -2102,16 +2286,16 @@
       </c>
       <c r="H24" s="37"/>
       <c r="I24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="K24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" s="18" t="s">
         <v>80</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -2123,20 +2307,20 @@
         <v>25</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H25" s="37"/>
       <c r="I25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="K25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L25" s="18" t="s">
         <v>83</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -2148,20 +2332,20 @@
         <v>26</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H26" s="37"/>
       <c r="I26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>57</v>
       </c>
       <c r="L26" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -2173,20 +2357,20 @@
         <v>27</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H27" s="37"/>
       <c r="I27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="K27" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="L27" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="L27" s="18" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="15" thickBot="1">
@@ -2198,96 +2382,96 @@
         <v>29</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H28" s="38"/>
       <c r="I28" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="J28" s="19" t="s">
         <v>92</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>93</v>
       </c>
       <c r="K28" s="19" t="s">
         <v>61</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="2:12">
       <c r="B29" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D29" s="26" t="s">
         <v>61</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H29" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="I29" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="J29" s="16" t="s">
         <v>114</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>115</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>61</v>
       </c>
       <c r="L29" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="2:12">
       <c r="B30" s="49"/>
       <c r="C30" s="28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H30" s="37"/>
       <c r="I30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J30" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="K30" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="L30" s="18" t="s">
         <v>118</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L30" s="18" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="31" spans="2:12">
       <c r="B31" s="49"/>
       <c r="C31" s="28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D31" s="28" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H31" s="37"/>
       <c r="I31" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J31" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="J31" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="K31" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L31" s="18" t="s">
         <v>58</v>
@@ -2296,76 +2480,76 @@
     <row r="32" spans="2:12">
       <c r="B32" s="49"/>
       <c r="C32" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="29" t="s">
         <v>175</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="E32" s="29" t="s">
-        <v>176</v>
       </c>
       <c r="H32" s="37"/>
       <c r="I32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="K32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L32" s="18" t="s">
         <v>123</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="L32" s="18" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="33" spans="2:12">
       <c r="B33" s="49"/>
       <c r="C33" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="E33" s="31" t="s">
         <v>178</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="E33" s="31" t="s">
-        <v>179</v>
       </c>
       <c r="H33" s="37"/>
       <c r="I33" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>57</v>
       </c>
       <c r="L33" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="2:12" ht="15" thickBot="1">
       <c r="B34" s="50"/>
       <c r="C34" s="32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H34" s="38"/>
       <c r="I34" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="J34" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="J34" s="19" t="s">
+      <c r="K34" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="L34" s="20" t="s">
         <v>129</v>
-      </c>
-      <c r="K34" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="L34" s="20" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2386,4 +2570,1610 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="9"/>
+      <c r="B1" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="9"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+    </row>
+    <row r="3" spans="1:12" ht="15" thickBot="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+    </row>
+    <row r="4" spans="1:12" ht="28.5" thickBot="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="9"/>
+      <c r="B5" s="48" t="s">
+        <v>202</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="9"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="9"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="9"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="9"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" thickBot="1">
+      <c r="A10" s="9"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="9"/>
+      <c r="B11" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="59" t="s">
+        <v>203</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="9"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="9"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="9"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="J14" s="82" t="s">
+        <v>196</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="18"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" thickBot="1">
+      <c r="A15" s="9"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="83" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="84" t="s">
+        <v>143</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" thickBot="1">
+      <c r="A16" s="9"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="83" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="84" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" thickBot="1">
+      <c r="A17" s="9"/>
+      <c r="B17" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="59" t="s">
+        <v>204</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15" thickBot="1">
+      <c r="A18" s="9"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15" thickBot="1">
+      <c r="A19" s="9"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="L19" s="18"/>
+    </row>
+    <row r="20" spans="1:18" ht="15" thickBot="1">
+      <c r="A20" s="9"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15" thickBot="1">
+      <c r="A21" s="9"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="69" t="s">
+        <v>190</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15" thickBot="1">
+      <c r="A22" s="9"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="69" t="s">
+        <v>192</v>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="9"/>
+      <c r="B23" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="9"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="9"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="9"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="9"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="L27" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15" thickBot="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15" thickBot="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" s="17"/>
+      <c r="O29" s="78" t="s">
+        <v>167</v>
+      </c>
+      <c r="P29" s="70" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q29" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="R29" s="72" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15" thickBot="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="L30" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="O30" s="79"/>
+      <c r="P30" s="73" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q30" s="74" t="s">
+        <v>71</v>
+      </c>
+      <c r="R30" s="75"/>
+    </row>
+    <row r="31" spans="1:18" ht="15" thickBot="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="O31" s="79"/>
+      <c r="P31" s="73" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q31" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="R31" s="75"/>
+    </row>
+    <row r="32" spans="1:18" ht="15" thickBot="1">
+      <c r="A32" s="9"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="O32" s="79"/>
+      <c r="P32" s="73" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q32" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="R32" s="75"/>
+    </row>
+    <row r="33" spans="1:18" ht="15" thickBot="1">
+      <c r="A33" s="9"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="E33" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="O33" s="79"/>
+      <c r="P33" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q33" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="R33" s="75"/>
+    </row>
+    <row r="34" spans="1:18" ht="15" thickBot="1">
+      <c r="A34" s="9"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="L34" s="20"/>
+      <c r="O34" s="80"/>
+      <c r="P34" s="76" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q34" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="R34" s="75" t="s">
+        <v>201</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="O29:O34"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="H17:H22"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="H23:H28"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="H29:H34"/>
+    <mergeCell ref="B1:E3"/>
+    <mergeCell ref="H1:L3"/>
+    <mergeCell ref="B5:B10"/>
+    <mergeCell ref="H5:H10"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="H11:H16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" thickBot="1">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+    </row>
+    <row r="4" spans="1:9" ht="28.5" thickBot="1">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1">
+      <c r="A6" s="37"/>
+      <c r="B6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1">
+      <c r="A7" s="37"/>
+      <c r="B7" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="H7" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="63" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1">
+      <c r="A8" s="37"/>
+      <c r="B8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="66" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1">
+      <c r="A9" s="37"/>
+      <c r="B9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="I9" s="66" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1">
+      <c r="A10" s="38"/>
+      <c r="B10" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="66" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15" thickBot="1">
+      <c r="A11" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" s="65" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15" thickBot="1">
+      <c r="A12" s="60"/>
+      <c r="B12" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="I12" s="68"/>
+    </row>
+    <row r="13" spans="1:9" ht="15" thickBot="1">
+      <c r="A13" s="60"/>
+      <c r="B13" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="I13" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1">
+      <c r="A14" s="60"/>
+      <c r="B14" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="G14" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="I14" s="65" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1">
+      <c r="A15" s="60"/>
+      <c r="B15" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" thickBot="1">
+      <c r="A16" s="61"/>
+      <c r="B16" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="49"/>
+      <c r="B18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="49"/>
+      <c r="B19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="49"/>
+      <c r="B20" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="28"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="49"/>
+      <c r="B21" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="28"/>
+    </row>
+    <row r="22" spans="1:5" ht="15" thickBot="1">
+      <c r="A22" s="50"/>
+      <c r="B22" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="28"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="37"/>
+      <c r="B24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="37"/>
+      <c r="B25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="37"/>
+      <c r="B26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="37"/>
+      <c r="B27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" thickBot="1">
+      <c r="A28" s="38"/>
+      <c r="B28" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="37"/>
+      <c r="B30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="37"/>
+      <c r="B31" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="37"/>
+      <c r="B32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="37"/>
+      <c r="B33" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" thickBot="1">
+      <c r="A34" s="38"/>
+      <c r="B34" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A1:E3"/>
+    <mergeCell ref="A5:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A29:A34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Listes LOUMAS phases1&2.xlsx
+++ b/Listes LOUMAS phases1&2.xlsx
@@ -1285,84 +1285,6 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1378,12 +1300,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1410,20 +1326,104 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1719,41 +1719,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52"/>
-      <c r="H1" s="39" t="s">
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="70"/>
+      <c r="H1" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
     </row>
     <row r="2" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="55"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
     </row>
     <row r="3" spans="2:12" ht="15" customHeight="1" thickBot="1">
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="58"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
     </row>
     <row r="4" spans="2:12" ht="28.5" thickBot="1">
       <c r="B4" s="10" t="s">
@@ -1785,7 +1785,7 @@
       </c>
     </row>
     <row r="5" spans="2:12">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="63" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -1797,7 +1797,7 @@
       <c r="E5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="54" t="s">
         <v>94</v>
       </c>
       <c r="I5" s="16" t="s">
@@ -1814,7 +1814,7 @@
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="B6" s="46"/>
+      <c r="B6" s="64"/>
       <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1824,7 +1824,7 @@
       <c r="E6" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="H6" s="37"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="6" t="s">
         <v>98</v>
       </c>
@@ -1839,7 +1839,7 @@
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="46"/>
+      <c r="B7" s="64"/>
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
@@ -1849,7 +1849,7 @@
       <c r="E7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="37"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="6" t="s">
         <v>101</v>
       </c>
@@ -1864,7 +1864,7 @@
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="46"/>
+      <c r="B8" s="64"/>
       <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
@@ -1874,7 +1874,7 @@
       <c r="E8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="37"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="6" t="s">
         <v>104</v>
       </c>
@@ -1889,7 +1889,7 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="46"/>
+      <c r="B9" s="64"/>
       <c r="C9" s="30" t="s">
         <v>15</v>
       </c>
@@ -1899,7 +1899,7 @@
       <c r="E9" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="37"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="6" t="s">
         <v>106</v>
       </c>
@@ -1914,7 +1914,7 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1">
-      <c r="B10" s="47"/>
+      <c r="B10" s="65"/>
       <c r="C10" s="15" t="s">
         <v>18</v>
       </c>
@@ -1924,7 +1924,7 @@
       <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="38"/>
+      <c r="H10" s="56"/>
       <c r="I10" s="19" t="s">
         <v>109</v>
       </c>
@@ -1939,7 +1939,7 @@
       </c>
     </row>
     <row r="11" spans="2:12">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="63" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1952,7 +1952,7 @@
         <v>166</v>
       </c>
       <c r="G11" s="9"/>
-      <c r="H11" s="59" t="s">
+      <c r="H11" s="77" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="16" t="s">
@@ -1969,7 +1969,7 @@
       </c>
     </row>
     <row r="12" spans="2:12">
-      <c r="B12" s="46"/>
+      <c r="B12" s="64"/>
       <c r="C12" s="5" t="s">
         <v>150</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>24</v>
       </c>
       <c r="G12" s="9"/>
-      <c r="H12" s="60"/>
+      <c r="H12" s="78"/>
       <c r="I12" s="6" t="s">
         <v>133</v>
       </c>
@@ -1995,7 +1995,7 @@
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="46"/>
+      <c r="B13" s="64"/>
       <c r="C13" s="5" t="s">
         <v>151</v>
       </c>
@@ -2005,7 +2005,7 @@
       <c r="E13" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="78"/>
       <c r="I13" s="6" t="s">
         <v>136</v>
       </c>
@@ -2020,7 +2020,7 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="46"/>
+      <c r="B14" s="64"/>
       <c r="C14" s="28" t="s">
         <v>152</v>
       </c>
@@ -2030,7 +2030,7 @@
       <c r="E14" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="78"/>
       <c r="I14" s="6" t="s">
         <v>139</v>
       </c>
@@ -2045,7 +2045,7 @@
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="46"/>
+      <c r="B15" s="64"/>
       <c r="C15" s="8" t="s">
         <v>153</v>
       </c>
@@ -2055,7 +2055,7 @@
       <c r="E15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="78"/>
       <c r="I15" s="6" t="s">
         <v>142</v>
       </c>
@@ -2070,7 +2070,7 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="15" thickBot="1">
-      <c r="B16" s="47"/>
+      <c r="B16" s="65"/>
       <c r="C16" s="32" t="s">
         <v>142</v>
       </c>
@@ -2080,7 +2080,7 @@
       <c r="E16" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="H16" s="61"/>
+      <c r="H16" s="79"/>
       <c r="I16" s="19" t="s">
         <v>145</v>
       </c>
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="17" spans="2:12">
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="66" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="14" t="s">
@@ -2107,7 +2107,7 @@
       <c r="E17" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="36" t="s">
+      <c r="H17" s="54" t="s">
         <v>54</v>
       </c>
       <c r="I17" s="16" t="s">
@@ -2124,7 +2124,7 @@
       </c>
     </row>
     <row r="18" spans="2:12">
-      <c r="B18" s="49"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
@@ -2134,7 +2134,7 @@
       <c r="E18" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="37"/>
+      <c r="H18" s="55"/>
       <c r="I18" s="6" t="s">
         <v>59</v>
       </c>
@@ -2149,7 +2149,7 @@
       </c>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="49"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
@@ -2159,7 +2159,7 @@
       <c r="E19" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="37"/>
+      <c r="H19" s="55"/>
       <c r="I19" s="6" t="s">
         <v>63</v>
       </c>
@@ -2170,7 +2170,7 @@
       <c r="L19" s="18"/>
     </row>
     <row r="20" spans="2:12">
-      <c r="B20" s="49"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="28" t="s">
         <v>37</v>
       </c>
@@ -2180,7 +2180,7 @@
       <c r="E20" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="H20" s="37"/>
+      <c r="H20" s="55"/>
       <c r="I20" s="6" t="s">
         <v>66</v>
       </c>
@@ -2195,7 +2195,7 @@
       </c>
     </row>
     <row r="21" spans="2:12">
-      <c r="B21" s="49"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="30" t="s">
         <v>38</v>
       </c>
@@ -2205,7 +2205,7 @@
       <c r="E21" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="H21" s="37"/>
+      <c r="H21" s="55"/>
       <c r="I21" s="6" t="s">
         <v>69</v>
       </c>
@@ -2220,7 +2220,7 @@
       </c>
     </row>
     <row r="22" spans="2:12" ht="15" thickBot="1">
-      <c r="B22" s="50"/>
+      <c r="B22" s="68"/>
       <c r="C22" s="32" t="s">
         <v>39</v>
       </c>
@@ -2230,7 +2230,7 @@
       <c r="E22" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="38"/>
+      <c r="H22" s="56"/>
       <c r="I22" s="19" t="s">
         <v>72</v>
       </c>
@@ -2245,7 +2245,7 @@
       </c>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="66" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="14" t="s">
@@ -2257,7 +2257,7 @@
       <c r="E23" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="36" t="s">
+      <c r="H23" s="54" t="s">
         <v>40</v>
       </c>
       <c r="I23" s="16" t="s">
@@ -2274,7 +2274,7 @@
       </c>
     </row>
     <row r="24" spans="2:12">
-      <c r="B24" s="49"/>
+      <c r="B24" s="67"/>
       <c r="C24" s="5" t="s">
         <v>43</v>
       </c>
@@ -2284,7 +2284,7 @@
       <c r="E24" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="37"/>
+      <c r="H24" s="55"/>
       <c r="I24" s="6" t="s">
         <v>78</v>
       </c>
@@ -2299,7 +2299,7 @@
       </c>
     </row>
     <row r="25" spans="2:12">
-      <c r="B25" s="49"/>
+      <c r="B25" s="67"/>
       <c r="C25" s="5" t="s">
         <v>45</v>
       </c>
@@ -2309,7 +2309,7 @@
       <c r="E25" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="H25" s="37"/>
+      <c r="H25" s="55"/>
       <c r="I25" s="6" t="s">
         <v>81</v>
       </c>
@@ -2324,7 +2324,7 @@
       </c>
     </row>
     <row r="26" spans="2:12">
-      <c r="B26" s="49"/>
+      <c r="B26" s="67"/>
       <c r="C26" s="5" t="s">
         <v>46</v>
       </c>
@@ -2334,7 +2334,7 @@
       <c r="E26" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="H26" s="37"/>
+      <c r="H26" s="55"/>
       <c r="I26" s="6" t="s">
         <v>84</v>
       </c>
@@ -2349,7 +2349,7 @@
       </c>
     </row>
     <row r="27" spans="2:12">
-      <c r="B27" s="49"/>
+      <c r="B27" s="67"/>
       <c r="C27" s="8" t="s">
         <v>47</v>
       </c>
@@ -2359,7 +2359,7 @@
       <c r="E27" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="H27" s="37"/>
+      <c r="H27" s="55"/>
       <c r="I27" s="6" t="s">
         <v>87</v>
       </c>
@@ -2374,7 +2374,7 @@
       </c>
     </row>
     <row r="28" spans="2:12" ht="15" thickBot="1">
-      <c r="B28" s="50"/>
+      <c r="B28" s="68"/>
       <c r="C28" s="15" t="s">
         <v>48</v>
       </c>
@@ -2384,7 +2384,7 @@
       <c r="E28" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="H28" s="38"/>
+      <c r="H28" s="56"/>
       <c r="I28" s="19" t="s">
         <v>91</v>
       </c>
@@ -2399,7 +2399,7 @@
       </c>
     </row>
     <row r="29" spans="2:12">
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="66" t="s">
         <v>167</v>
       </c>
       <c r="C29" s="26" t="s">
@@ -2411,7 +2411,7 @@
       <c r="E29" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="H29" s="36" t="s">
+      <c r="H29" s="54" t="s">
         <v>112</v>
       </c>
       <c r="I29" s="16" t="s">
@@ -2428,7 +2428,7 @@
       </c>
     </row>
     <row r="30" spans="2:12">
-      <c r="B30" s="49"/>
+      <c r="B30" s="67"/>
       <c r="C30" s="28" t="s">
         <v>171</v>
       </c>
@@ -2438,7 +2438,7 @@
       <c r="E30" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="H30" s="37"/>
+      <c r="H30" s="55"/>
       <c r="I30" s="6" t="s">
         <v>116</v>
       </c>
@@ -2453,7 +2453,7 @@
       </c>
     </row>
     <row r="31" spans="2:12">
-      <c r="B31" s="49"/>
+      <c r="B31" s="67"/>
       <c r="C31" s="28" t="s">
         <v>172</v>
       </c>
@@ -2463,7 +2463,7 @@
       <c r="E31" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="H31" s="37"/>
+      <c r="H31" s="55"/>
       <c r="I31" s="6" t="s">
         <v>119</v>
       </c>
@@ -2478,7 +2478,7 @@
       </c>
     </row>
     <row r="32" spans="2:12">
-      <c r="B32" s="49"/>
+      <c r="B32" s="67"/>
       <c r="C32" s="28" t="s">
         <v>174</v>
       </c>
@@ -2488,7 +2488,7 @@
       <c r="E32" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="H32" s="37"/>
+      <c r="H32" s="55"/>
       <c r="I32" s="6" t="s">
         <v>121</v>
       </c>
@@ -2503,7 +2503,7 @@
       </c>
     </row>
     <row r="33" spans="2:12">
-      <c r="B33" s="49"/>
+      <c r="B33" s="67"/>
       <c r="C33" s="30" t="s">
         <v>177</v>
       </c>
@@ -2513,7 +2513,7 @@
       <c r="E33" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="H33" s="37"/>
+      <c r="H33" s="55"/>
       <c r="I33" s="6" t="s">
         <v>124</v>
       </c>
@@ -2528,7 +2528,7 @@
       </c>
     </row>
     <row r="34" spans="2:12" ht="15" thickBot="1">
-      <c r="B34" s="50"/>
+      <c r="B34" s="68"/>
       <c r="C34" s="32" t="s">
         <v>127</v>
       </c>
@@ -2538,7 +2538,7 @@
       <c r="E34" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="H34" s="38"/>
+      <c r="H34" s="56"/>
       <c r="I34" s="19" t="s">
         <v>127</v>
       </c>
@@ -2593,49 +2593,49 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="9"/>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="70"/>
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="9"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="55"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1">
       <c r="A3" s="9"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="58"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
     </row>
     <row r="4" spans="1:12" ht="28.5" thickBot="1">
       <c r="A4" s="9"/>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="9"/>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="66" t="s">
         <v>202</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="54" t="s">
         <v>202</v>
       </c>
       <c r="I5" s="16" t="s">
@@ -2703,7 +2703,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="9"/>
-      <c r="B6" s="49"/>
+      <c r="B6" s="67"/>
       <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="37"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="6" t="s">
         <v>98</v>
       </c>
@@ -2731,7 +2731,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="9"/>
-      <c r="B7" s="49"/>
+      <c r="B7" s="67"/>
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="37"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="6" t="s">
         <v>101</v>
       </c>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="9"/>
-      <c r="B8" s="49"/>
+      <c r="B8" s="67"/>
       <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="37"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="6" t="s">
         <v>104</v>
       </c>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="9"/>
-      <c r="B9" s="49"/>
+      <c r="B9" s="67"/>
       <c r="C9" s="30" t="s">
         <v>15</v>
       </c>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="37"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="6" t="s">
         <v>106</v>
       </c>
@@ -2815,7 +2815,7 @@
     </row>
     <row r="10" spans="1:12" ht="15" thickBot="1">
       <c r="A10" s="9"/>
-      <c r="B10" s="50"/>
+      <c r="B10" s="68"/>
       <c r="C10" s="15" t="s">
         <v>18</v>
       </c>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="38"/>
+      <c r="H10" s="56"/>
       <c r="I10" s="19" t="s">
         <v>109</v>
       </c>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="9"/>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="66" t="s">
         <v>203</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="59" t="s">
+      <c r="H11" s="77" t="s">
         <v>203</v>
       </c>
       <c r="I11" s="14" t="s">
@@ -2875,7 +2875,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="9"/>
-      <c r="B12" s="49"/>
+      <c r="B12" s="67"/>
       <c r="C12" s="5" t="s">
         <v>150</v>
       </c>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="60"/>
+      <c r="H12" s="78"/>
       <c r="I12" s="5" t="s">
         <v>133</v>
       </c>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="9"/>
-      <c r="B13" s="49"/>
+      <c r="B13" s="67"/>
       <c r="C13" s="5" t="s">
         <v>151</v>
       </c>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="60"/>
+      <c r="H13" s="78"/>
       <c r="I13" s="5" t="s">
         <v>193</v>
       </c>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="9"/>
-      <c r="B14" s="49"/>
+      <c r="B14" s="67"/>
       <c r="C14" s="28" t="s">
         <v>152</v>
       </c>
@@ -2943,11 +2943,11 @@
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="81" t="s">
+      <c r="H14" s="78"/>
+      <c r="I14" s="50" t="s">
         <v>194</v>
       </c>
-      <c r="J14" s="82" t="s">
+      <c r="J14" s="51" t="s">
         <v>196</v>
       </c>
       <c r="K14" s="6" t="s">
@@ -2957,7 +2957,7 @@
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1">
       <c r="A15" s="9"/>
-      <c r="B15" s="49"/>
+      <c r="B15" s="67"/>
       <c r="C15" s="8" t="s">
         <v>153</v>
       </c>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="83" t="s">
+      <c r="H15" s="78"/>
+      <c r="I15" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="J15" s="84" t="s">
+      <c r="J15" s="53" t="s">
         <v>143</v>
       </c>
       <c r="K15" s="6" t="s">
@@ -2985,7 +2985,7 @@
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1">
       <c r="A16" s="9"/>
-      <c r="B16" s="50"/>
+      <c r="B16" s="68"/>
       <c r="C16" s="32" t="s">
         <v>142</v>
       </c>
@@ -2997,11 +2997,11 @@
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="83" t="s">
+      <c r="H16" s="79"/>
+      <c r="I16" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="84" t="s">
+      <c r="J16" s="53" t="s">
         <v>146</v>
       </c>
       <c r="K16" s="19" t="s">
@@ -3013,7 +3013,7 @@
     </row>
     <row r="17" spans="1:18" ht="15" thickBot="1">
       <c r="A17" s="9"/>
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="66" t="s">
         <v>204</v>
       </c>
       <c r="C17" s="14" t="s">
@@ -3022,12 +3022,12 @@
       <c r="D17" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="66" t="s">
+      <c r="E17" s="40" t="s">
         <v>32</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="59" t="s">
+      <c r="H17" s="77" t="s">
         <v>204</v>
       </c>
       <c r="I17" s="16" t="s">
@@ -3045,19 +3045,19 @@
     </row>
     <row r="18" spans="1:18" ht="15" thickBot="1">
       <c r="A18" s="9"/>
-      <c r="B18" s="49"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="66" t="s">
+      <c r="E18" s="40" t="s">
         <v>184</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="60"/>
+      <c r="H18" s="78"/>
       <c r="I18" s="6" t="s">
         <v>59</v>
       </c>
@@ -3073,19 +3073,19 @@
     </row>
     <row r="19" spans="1:18" ht="15" thickBot="1">
       <c r="A19" s="9"/>
-      <c r="B19" s="49"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="66" t="s">
+      <c r="E19" s="40" t="s">
         <v>185</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="60"/>
+      <c r="H19" s="78"/>
       <c r="I19" s="6" t="s">
         <v>197</v>
       </c>
@@ -3097,19 +3097,19 @@
     </row>
     <row r="20" spans="1:18" ht="15" thickBot="1">
       <c r="A20" s="9"/>
-      <c r="B20" s="49"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="28" t="s">
         <v>186</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="41" t="s">
         <v>187</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-      <c r="H20" s="60"/>
+      <c r="H20" s="78"/>
       <c r="I20" s="6" t="s">
         <v>66</v>
       </c>
@@ -3125,19 +3125,19 @@
     </row>
     <row r="21" spans="1:18" ht="15" thickBot="1">
       <c r="A21" s="9"/>
-      <c r="B21" s="49"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="28" t="s">
         <v>189</v>
       </c>
       <c r="D21" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="69" t="s">
+      <c r="E21" s="41" t="s">
         <v>190</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
-      <c r="H21" s="60"/>
+      <c r="H21" s="78"/>
       <c r="I21" s="6" t="s">
         <v>69</v>
       </c>
@@ -3153,19 +3153,19 @@
     </row>
     <row r="22" spans="1:18" ht="15" thickBot="1">
       <c r="A22" s="9"/>
-      <c r="B22" s="50"/>
+      <c r="B22" s="68"/>
       <c r="C22" s="28" t="s">
         <v>191</v>
       </c>
       <c r="D22" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="69" t="s">
+      <c r="E22" s="41" t="s">
         <v>192</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
-      <c r="H22" s="61"/>
+      <c r="H22" s="79"/>
       <c r="I22" s="19" t="s">
         <v>72</v>
       </c>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="9"/>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="66" t="s">
         <v>205</v>
       </c>
       <c r="C23" s="14" t="s">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="36" t="s">
+      <c r="H23" s="54" t="s">
         <v>205</v>
       </c>
       <c r="I23" s="16" t="s">
@@ -3213,7 +3213,7 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="9"/>
-      <c r="B24" s="49"/>
+      <c r="B24" s="67"/>
       <c r="C24" s="5" t="s">
         <v>43</v>
       </c>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="37"/>
+      <c r="H24" s="55"/>
       <c r="I24" s="6" t="s">
         <v>78</v>
       </c>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="9"/>
-      <c r="B25" s="49"/>
+      <c r="B25" s="67"/>
       <c r="C25" s="5" t="s">
         <v>45</v>
       </c>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="37"/>
+      <c r="H25" s="55"/>
       <c r="I25" s="6" t="s">
         <v>81</v>
       </c>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="9"/>
-      <c r="B26" s="49"/>
+      <c r="B26" s="67"/>
       <c r="C26" s="5" t="s">
         <v>46</v>
       </c>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
-      <c r="H26" s="37"/>
+      <c r="H26" s="55"/>
       <c r="I26" s="6" t="s">
         <v>84</v>
       </c>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="9"/>
-      <c r="B27" s="49"/>
+      <c r="B27" s="67"/>
       <c r="C27" s="8" t="s">
         <v>47</v>
       </c>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="H27" s="37"/>
+      <c r="H27" s="55"/>
       <c r="I27" s="6" t="s">
         <v>87</v>
       </c>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="28" spans="1:18" ht="15" thickBot="1">
       <c r="A28" s="9"/>
-      <c r="B28" s="50"/>
+      <c r="B28" s="68"/>
       <c r="C28" s="15" t="s">
         <v>48</v>
       </c>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="38"/>
+      <c r="H28" s="56"/>
       <c r="I28" s="19" t="s">
         <v>91</v>
       </c>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="29" spans="1:18" ht="15" thickBot="1">
       <c r="A29" s="9"/>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="66" t="s">
         <v>206</v>
       </c>
       <c r="C29" s="26" t="s">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="36" t="s">
+      <c r="H29" s="54" t="s">
         <v>206</v>
       </c>
       <c r="I29" s="16" t="s">
@@ -3380,22 +3380,22 @@
         <v>61</v>
       </c>
       <c r="L29" s="17"/>
-      <c r="O29" s="78" t="s">
+      <c r="O29" s="80" t="s">
         <v>167</v>
       </c>
-      <c r="P29" s="70" t="s">
+      <c r="P29" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="Q29" s="71" t="s">
+      <c r="Q29" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="R29" s="72" t="s">
+      <c r="R29" s="44" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15" thickBot="1">
       <c r="A30" s="9"/>
-      <c r="B30" s="49"/>
+      <c r="B30" s="67"/>
       <c r="C30" s="28" t="s">
         <v>171</v>
       </c>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="37"/>
+      <c r="H30" s="55"/>
       <c r="I30" s="6" t="s">
         <v>116</v>
       </c>
@@ -3420,18 +3420,18 @@
       <c r="L30" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="O30" s="79"/>
-      <c r="P30" s="73" t="s">
+      <c r="O30" s="81"/>
+      <c r="P30" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="Q30" s="74" t="s">
+      <c r="Q30" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="R30" s="75"/>
+      <c r="R30" s="47"/>
     </row>
     <row r="31" spans="1:18" ht="15" thickBot="1">
       <c r="A31" s="9"/>
-      <c r="B31" s="49"/>
+      <c r="B31" s="67"/>
       <c r="C31" s="28" t="s">
         <v>172</v>
       </c>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="37"/>
+      <c r="H31" s="55"/>
       <c r="I31" s="6" t="s">
         <v>119</v>
       </c>
@@ -3456,18 +3456,18 @@
       <c r="L31" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="O31" s="79"/>
-      <c r="P31" s="73" t="s">
+      <c r="O31" s="81"/>
+      <c r="P31" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="Q31" s="74" t="s">
+      <c r="Q31" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="R31" s="75"/>
+      <c r="R31" s="47"/>
     </row>
     <row r="32" spans="1:18" ht="15" thickBot="1">
       <c r="A32" s="9"/>
-      <c r="B32" s="49"/>
+      <c r="B32" s="67"/>
       <c r="C32" s="28" t="s">
         <v>174</v>
       </c>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="37"/>
+      <c r="H32" s="55"/>
       <c r="I32" s="6" t="s">
         <v>121</v>
       </c>
@@ -3492,18 +3492,18 @@
       <c r="L32" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="O32" s="79"/>
-      <c r="P32" s="73" t="s">
+      <c r="O32" s="81"/>
+      <c r="P32" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="Q32" s="74" t="s">
+      <c r="Q32" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="R32" s="75"/>
+      <c r="R32" s="47"/>
     </row>
     <row r="33" spans="1:18" ht="15" thickBot="1">
       <c r="A33" s="9"/>
-      <c r="B33" s="49"/>
+      <c r="B33" s="67"/>
       <c r="C33" s="30" t="s">
         <v>177</v>
       </c>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
-      <c r="H33" s="37"/>
+      <c r="H33" s="55"/>
       <c r="I33" s="6" t="s">
         <v>124</v>
       </c>
@@ -3528,18 +3528,18 @@
       <c r="L33" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="O33" s="79"/>
-      <c r="P33" s="73" t="s">
+      <c r="O33" s="81"/>
+      <c r="P33" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="Q33" s="74" t="s">
+      <c r="Q33" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="R33" s="75"/>
+      <c r="R33" s="47"/>
     </row>
     <row r="34" spans="1:18" ht="15" thickBot="1">
       <c r="A34" s="9"/>
-      <c r="B34" s="50"/>
+      <c r="B34" s="68"/>
       <c r="C34" s="32" t="s">
         <v>127</v>
       </c>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="38"/>
+      <c r="H34" s="56"/>
       <c r="I34" s="19" t="s">
         <v>200</v>
       </c>
@@ -3562,19 +3562,25 @@
         <v>64</v>
       </c>
       <c r="L34" s="20"/>
-      <c r="O34" s="80"/>
-      <c r="P34" s="76" t="s">
+      <c r="O34" s="82"/>
+      <c r="P34" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="Q34" s="77" t="s">
+      <c r="Q34" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="R34" s="75" t="s">
+      <c r="R34" s="47" t="s">
         <v>201</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:E3"/>
+    <mergeCell ref="H1:L3"/>
+    <mergeCell ref="B5:B10"/>
+    <mergeCell ref="H5:H10"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="H11:H16"/>
     <mergeCell ref="O29:O34"/>
     <mergeCell ref="B17:B22"/>
     <mergeCell ref="H17:H22"/>
@@ -3582,12 +3588,6 @@
     <mergeCell ref="H23:H28"/>
     <mergeCell ref="B29:B34"/>
     <mergeCell ref="H29:H34"/>
-    <mergeCell ref="B1:E3"/>
-    <mergeCell ref="H1:L3"/>
-    <mergeCell ref="B5:B10"/>
-    <mergeCell ref="H5:H10"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="H11:H16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3609,27 +3609,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
     </row>
     <row r="4" spans="1:9" ht="28.5" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -3649,7 +3649,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="54" t="s">
         <v>94</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -3666,7 +3666,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1">
-      <c r="A6" s="37"/>
+      <c r="A6" s="55"/>
       <c r="B6" s="6" t="s">
         <v>98</v>
       </c>
@@ -3681,7 +3681,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1">
-      <c r="A7" s="37"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="6" t="s">
         <v>101</v>
       </c>
@@ -3694,18 +3694,18 @@
       <c r="E7" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="H7" s="63" t="s">
+      <c r="H7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="63" t="s">
+      <c r="I7" s="37" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1">
-      <c r="A8" s="37"/>
+      <c r="A8" s="55"/>
       <c r="B8" s="6" t="s">
         <v>104</v>
       </c>
@@ -3718,18 +3718,18 @@
       <c r="E8" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="65" t="s">
+      <c r="H8" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="66" t="s">
+      <c r="I8" s="40" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" thickBot="1">
-      <c r="A9" s="37"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="6" t="s">
         <v>106</v>
       </c>
@@ -3742,18 +3742,18 @@
       <c r="E9" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="H9" s="65" t="s">
+      <c r="H9" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="I9" s="66" t="s">
+      <c r="I9" s="40" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1">
-      <c r="A10" s="38"/>
+      <c r="A10" s="56"/>
       <c r="B10" s="19" t="s">
         <v>109</v>
       </c>
@@ -3766,18 +3766,18 @@
       <c r="E10" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="65" t="s">
+      <c r="H10" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="66" t="s">
+      <c r="I10" s="40" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" thickBot="1">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="77" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -3792,18 +3792,18 @@
       <c r="E11" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="65" t="s">
+      <c r="H11" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="I11" s="65" t="s">
+      <c r="I11" s="39" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" thickBot="1">
-      <c r="A12" s="60"/>
+      <c r="A12" s="78"/>
       <c r="B12" s="5" t="s">
         <v>133</v>
       </c>
@@ -3816,16 +3816,16 @@
       <c r="E12" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="H12" s="83" t="s">
         <v>188</v>
       </c>
-      <c r="I12" s="68"/>
+      <c r="I12" s="84"/>
     </row>
     <row r="13" spans="1:9" ht="15" thickBot="1">
-      <c r="A13" s="60"/>
+      <c r="A13" s="78"/>
       <c r="B13" s="5" t="s">
         <v>193</v>
       </c>
@@ -3838,18 +3838,18 @@
       <c r="E13" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="65" t="s">
+      <c r="H13" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="I13" s="65" t="s">
+      <c r="I13" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1">
-      <c r="A14" s="60"/>
+      <c r="A14" s="78"/>
       <c r="B14" s="28" t="s">
         <v>194</v>
       </c>
@@ -3860,18 +3860,18 @@
         <v>57</v>
       </c>
       <c r="E14" s="18"/>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="65" t="s">
+      <c r="H14" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="I14" s="65" t="s">
+      <c r="I14" s="39" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1">
-      <c r="A15" s="60"/>
+      <c r="A15" s="78"/>
       <c r="B15" s="32" t="s">
         <v>142</v>
       </c>
@@ -3886,7 +3886,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" thickBot="1">
-      <c r="A16" s="61"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="32" t="s">
         <v>145</v>
       </c>
@@ -3901,7 +3901,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="66" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="14" t="s">
@@ -3916,7 +3916,7 @@
       <c r="E17" s="14"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="49"/>
+      <c r="A18" s="67"/>
       <c r="B18" s="5" t="s">
         <v>33</v>
       </c>
@@ -3929,7 +3929,7 @@
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="49"/>
+      <c r="A19" s="67"/>
       <c r="B19" s="5" t="s">
         <v>35</v>
       </c>
@@ -3942,7 +3942,7 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="49"/>
+      <c r="A20" s="67"/>
       <c r="B20" s="28" t="s">
         <v>186</v>
       </c>
@@ -3955,7 +3955,7 @@
       <c r="E20" s="28"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="49"/>
+      <c r="A21" s="67"/>
       <c r="B21" s="28" t="s">
         <v>189</v>
       </c>
@@ -3968,7 +3968,7 @@
       <c r="E21" s="28"/>
     </row>
     <row r="22" spans="1:5" ht="15" thickBot="1">
-      <c r="A22" s="50"/>
+      <c r="A22" s="68"/>
       <c r="B22" s="28" t="s">
         <v>191</v>
       </c>
@@ -3981,7 +3981,7 @@
       <c r="E22" s="28"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="54" t="s">
         <v>40</v>
       </c>
       <c r="B23" s="16" t="s">
@@ -3998,7 +3998,7 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="37"/>
+      <c r="A24" s="55"/>
       <c r="B24" s="6" t="s">
         <v>78</v>
       </c>
@@ -4013,7 +4013,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="37"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="6" t="s">
         <v>81</v>
       </c>
@@ -4028,7 +4028,7 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="37"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="6" t="s">
         <v>84</v>
       </c>
@@ -4043,7 +4043,7 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="37"/>
+      <c r="A27" s="55"/>
       <c r="B27" s="6" t="s">
         <v>87</v>
       </c>
@@ -4058,7 +4058,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" thickBot="1">
-      <c r="A28" s="38"/>
+      <c r="A28" s="56"/>
       <c r="B28" s="19" t="s">
         <v>91</v>
       </c>
@@ -4073,7 +4073,7 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="54" t="s">
         <v>112</v>
       </c>
       <c r="B29" s="16" t="s">
@@ -4090,7 +4090,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="37"/>
+      <c r="A30" s="55"/>
       <c r="B30" s="6" t="s">
         <v>116</v>
       </c>
@@ -4105,7 +4105,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="37"/>
+      <c r="A31" s="55"/>
       <c r="B31" s="6" t="s">
         <v>119</v>
       </c>
@@ -4120,7 +4120,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="37"/>
+      <c r="A32" s="55"/>
       <c r="B32" s="6" t="s">
         <v>121</v>
       </c>
@@ -4135,7 +4135,7 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="37"/>
+      <c r="A33" s="55"/>
       <c r="B33" s="6" t="s">
         <v>124</v>
       </c>
@@ -4150,7 +4150,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" thickBot="1">
-      <c r="A34" s="38"/>
+      <c r="A34" s="56"/>
       <c r="B34" s="19" t="s">
         <v>127</v>
       </c>
@@ -4166,13 +4166,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A29:A34"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="A1:E3"/>
     <mergeCell ref="A5:A10"/>
     <mergeCell ref="A11:A16"/>
     <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="A29:A34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Listes LOUMAS phases1&2.xlsx
+++ b/Listes LOUMAS phases1&2.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="216">
   <si>
     <t>DRV</t>
   </si>
@@ -667,6 +667,33 @@
   </si>
   <si>
     <t>DRS</t>
+  </si>
+  <si>
+    <t>14,30745°N; 15,29500°O</t>
+  </si>
+  <si>
+    <t>BONDALA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4336765, -11.8780003 </t>
+  </si>
+  <si>
+    <t>SALEMATA</t>
+  </si>
+  <si>
+    <t>12.635260, -12.819908</t>
+  </si>
+  <si>
+    <t>80km</t>
+  </si>
+  <si>
+    <t>GUEMEDJIE</t>
+  </si>
+  <si>
+    <t>12.558485, -12.178625</t>
+  </si>
+  <si>
+    <t>MOURAN</t>
   </si>
 </sst>
 </file>
@@ -789,7 +816,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1201,24 +1228,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1303,30 +1317,6 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1407,15 +1397,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1719,41 +1700,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="70"/>
-      <c r="H1" s="57" t="s">
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="62"/>
+      <c r="H1" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
     </row>
     <row r="2" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B2" s="71"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="73"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
     </row>
     <row r="3" spans="2:12" ht="15" customHeight="1" thickBot="1">
-      <c r="B3" s="74"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="68"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
     </row>
     <row r="4" spans="2:12" ht="28.5" thickBot="1">
       <c r="B4" s="10" t="s">
@@ -1785,7 +1766,7 @@
       </c>
     </row>
     <row r="5" spans="2:12">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="55" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -1797,7 +1778,7 @@
       <c r="E5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="54" t="s">
+      <c r="H5" s="46" t="s">
         <v>94</v>
       </c>
       <c r="I5" s="16" t="s">
@@ -1814,7 +1795,7 @@
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="B6" s="64"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1824,7 +1805,7 @@
       <c r="E6" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="H6" s="55"/>
+      <c r="H6" s="47"/>
       <c r="I6" s="6" t="s">
         <v>98</v>
       </c>
@@ -1839,7 +1820,7 @@
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="64"/>
+      <c r="B7" s="56"/>
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
@@ -1849,7 +1830,7 @@
       <c r="E7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="55"/>
+      <c r="H7" s="47"/>
       <c r="I7" s="6" t="s">
         <v>101</v>
       </c>
@@ -1864,7 +1845,7 @@
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="64"/>
+      <c r="B8" s="56"/>
       <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
@@ -1874,7 +1855,7 @@
       <c r="E8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="55"/>
+      <c r="H8" s="47"/>
       <c r="I8" s="6" t="s">
         <v>104</v>
       </c>
@@ -1889,7 +1870,7 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="64"/>
+      <c r="B9" s="56"/>
       <c r="C9" s="30" t="s">
         <v>15</v>
       </c>
@@ -1899,7 +1880,7 @@
       <c r="E9" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="55"/>
+      <c r="H9" s="47"/>
       <c r="I9" s="6" t="s">
         <v>106</v>
       </c>
@@ -1914,7 +1895,7 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1">
-      <c r="B10" s="65"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="15" t="s">
         <v>18</v>
       </c>
@@ -1924,7 +1905,7 @@
       <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="56"/>
+      <c r="H10" s="48"/>
       <c r="I10" s="19" t="s">
         <v>109</v>
       </c>
@@ -1939,7 +1920,7 @@
       </c>
     </row>
     <row r="11" spans="2:12">
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="55" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1952,7 +1933,7 @@
         <v>166</v>
       </c>
       <c r="G11" s="9"/>
-      <c r="H11" s="77" t="s">
+      <c r="H11" s="69" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="16" t="s">
@@ -1969,7 +1950,7 @@
       </c>
     </row>
     <row r="12" spans="2:12">
-      <c r="B12" s="64"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="5" t="s">
         <v>150</v>
       </c>
@@ -1980,7 +1961,7 @@
         <v>24</v>
       </c>
       <c r="G12" s="9"/>
-      <c r="H12" s="78"/>
+      <c r="H12" s="70"/>
       <c r="I12" s="6" t="s">
         <v>133</v>
       </c>
@@ -1995,7 +1976,7 @@
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="64"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="5" t="s">
         <v>151</v>
       </c>
@@ -2005,7 +1986,7 @@
       <c r="E13" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="H13" s="78"/>
+      <c r="H13" s="70"/>
       <c r="I13" s="6" t="s">
         <v>136</v>
       </c>
@@ -2020,7 +2001,7 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="64"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="28" t="s">
         <v>152</v>
       </c>
@@ -2030,7 +2011,7 @@
       <c r="E14" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="H14" s="78"/>
+      <c r="H14" s="70"/>
       <c r="I14" s="6" t="s">
         <v>139</v>
       </c>
@@ -2045,7 +2026,7 @@
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="64"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="8" t="s">
         <v>153</v>
       </c>
@@ -2055,7 +2036,7 @@
       <c r="E15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="78"/>
+      <c r="H15" s="70"/>
       <c r="I15" s="6" t="s">
         <v>142</v>
       </c>
@@ -2070,7 +2051,7 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="15" thickBot="1">
-      <c r="B16" s="65"/>
+      <c r="B16" s="57"/>
       <c r="C16" s="32" t="s">
         <v>142</v>
       </c>
@@ -2080,7 +2061,7 @@
       <c r="E16" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="H16" s="79"/>
+      <c r="H16" s="71"/>
       <c r="I16" s="19" t="s">
         <v>145</v>
       </c>
@@ -2095,7 +2076,7 @@
       </c>
     </row>
     <row r="17" spans="2:12">
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="58" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="14" t="s">
@@ -2107,7 +2088,7 @@
       <c r="E17" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="54" t="s">
+      <c r="H17" s="46" t="s">
         <v>54</v>
       </c>
       <c r="I17" s="16" t="s">
@@ -2124,7 +2105,7 @@
       </c>
     </row>
     <row r="18" spans="2:12">
-      <c r="B18" s="67"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
@@ -2134,7 +2115,7 @@
       <c r="E18" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="55"/>
+      <c r="H18" s="47"/>
       <c r="I18" s="6" t="s">
         <v>59</v>
       </c>
@@ -2149,7 +2130,7 @@
       </c>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="67"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
@@ -2159,7 +2140,7 @@
       <c r="E19" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="55"/>
+      <c r="H19" s="47"/>
       <c r="I19" s="6" t="s">
         <v>63</v>
       </c>
@@ -2170,7 +2151,7 @@
       <c r="L19" s="18"/>
     </row>
     <row r="20" spans="2:12">
-      <c r="B20" s="67"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="28" t="s">
         <v>37</v>
       </c>
@@ -2180,7 +2161,7 @@
       <c r="E20" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="H20" s="55"/>
+      <c r="H20" s="47"/>
       <c r="I20" s="6" t="s">
         <v>66</v>
       </c>
@@ -2195,7 +2176,7 @@
       </c>
     </row>
     <row r="21" spans="2:12">
-      <c r="B21" s="67"/>
+      <c r="B21" s="59"/>
       <c r="C21" s="30" t="s">
         <v>38</v>
       </c>
@@ -2205,7 +2186,7 @@
       <c r="E21" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="H21" s="55"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="6" t="s">
         <v>69</v>
       </c>
@@ -2220,7 +2201,7 @@
       </c>
     </row>
     <row r="22" spans="2:12" ht="15" thickBot="1">
-      <c r="B22" s="68"/>
+      <c r="B22" s="60"/>
       <c r="C22" s="32" t="s">
         <v>39</v>
       </c>
@@ -2230,7 +2211,7 @@
       <c r="E22" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="56"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="19" t="s">
         <v>72</v>
       </c>
@@ -2245,7 +2226,7 @@
       </c>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="66" t="s">
+      <c r="B23" s="58" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="14" t="s">
@@ -2257,7 +2238,7 @@
       <c r="E23" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="54" t="s">
+      <c r="H23" s="46" t="s">
         <v>40</v>
       </c>
       <c r="I23" s="16" t="s">
@@ -2274,7 +2255,7 @@
       </c>
     </row>
     <row r="24" spans="2:12">
-      <c r="B24" s="67"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="5" t="s">
         <v>43</v>
       </c>
@@ -2284,7 +2265,7 @@
       <c r="E24" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="55"/>
+      <c r="H24" s="47"/>
       <c r="I24" s="6" t="s">
         <v>78</v>
       </c>
@@ -2299,7 +2280,7 @@
       </c>
     </row>
     <row r="25" spans="2:12">
-      <c r="B25" s="67"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="5" t="s">
         <v>45</v>
       </c>
@@ -2309,7 +2290,7 @@
       <c r="E25" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="H25" s="55"/>
+      <c r="H25" s="47"/>
       <c r="I25" s="6" t="s">
         <v>81</v>
       </c>
@@ -2324,7 +2305,7 @@
       </c>
     </row>
     <row r="26" spans="2:12">
-      <c r="B26" s="67"/>
+      <c r="B26" s="59"/>
       <c r="C26" s="5" t="s">
         <v>46</v>
       </c>
@@ -2334,7 +2315,7 @@
       <c r="E26" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="H26" s="55"/>
+      <c r="H26" s="47"/>
       <c r="I26" s="6" t="s">
         <v>84</v>
       </c>
@@ -2349,7 +2330,7 @@
       </c>
     </row>
     <row r="27" spans="2:12">
-      <c r="B27" s="67"/>
+      <c r="B27" s="59"/>
       <c r="C27" s="8" t="s">
         <v>47</v>
       </c>
@@ -2359,7 +2340,7 @@
       <c r="E27" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="H27" s="55"/>
+      <c r="H27" s="47"/>
       <c r="I27" s="6" t="s">
         <v>87</v>
       </c>
@@ -2374,7 +2355,7 @@
       </c>
     </row>
     <row r="28" spans="2:12" ht="15" thickBot="1">
-      <c r="B28" s="68"/>
+      <c r="B28" s="60"/>
       <c r="C28" s="15" t="s">
         <v>48</v>
       </c>
@@ -2384,7 +2365,7 @@
       <c r="E28" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="H28" s="56"/>
+      <c r="H28" s="48"/>
       <c r="I28" s="19" t="s">
         <v>91</v>
       </c>
@@ -2399,7 +2380,7 @@
       </c>
     </row>
     <row r="29" spans="2:12">
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="58" t="s">
         <v>167</v>
       </c>
       <c r="C29" s="26" t="s">
@@ -2411,7 +2392,7 @@
       <c r="E29" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="H29" s="54" t="s">
+      <c r="H29" s="46" t="s">
         <v>112</v>
       </c>
       <c r="I29" s="16" t="s">
@@ -2428,7 +2409,7 @@
       </c>
     </row>
     <row r="30" spans="2:12">
-      <c r="B30" s="67"/>
+      <c r="B30" s="59"/>
       <c r="C30" s="28" t="s">
         <v>171</v>
       </c>
@@ -2438,7 +2419,7 @@
       <c r="E30" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="H30" s="55"/>
+      <c r="H30" s="47"/>
       <c r="I30" s="6" t="s">
         <v>116</v>
       </c>
@@ -2453,7 +2434,7 @@
       </c>
     </row>
     <row r="31" spans="2:12">
-      <c r="B31" s="67"/>
+      <c r="B31" s="59"/>
       <c r="C31" s="28" t="s">
         <v>172</v>
       </c>
@@ -2463,7 +2444,7 @@
       <c r="E31" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="H31" s="55"/>
+      <c r="H31" s="47"/>
       <c r="I31" s="6" t="s">
         <v>119</v>
       </c>
@@ -2478,7 +2459,7 @@
       </c>
     </row>
     <row r="32" spans="2:12">
-      <c r="B32" s="67"/>
+      <c r="B32" s="59"/>
       <c r="C32" s="28" t="s">
         <v>174</v>
       </c>
@@ -2488,7 +2469,7 @@
       <c r="E32" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="H32" s="55"/>
+      <c r="H32" s="47"/>
       <c r="I32" s="6" t="s">
         <v>121</v>
       </c>
@@ -2503,7 +2484,7 @@
       </c>
     </row>
     <row r="33" spans="2:12">
-      <c r="B33" s="67"/>
+      <c r="B33" s="59"/>
       <c r="C33" s="30" t="s">
         <v>177</v>
       </c>
@@ -2513,7 +2494,7 @@
       <c r="E33" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="H33" s="55"/>
+      <c r="H33" s="47"/>
       <c r="I33" s="6" t="s">
         <v>124</v>
       </c>
@@ -2528,7 +2509,7 @@
       </c>
     </row>
     <row r="34" spans="2:12" ht="15" thickBot="1">
-      <c r="B34" s="68"/>
+      <c r="B34" s="60"/>
       <c r="C34" s="32" t="s">
         <v>127</v>
       </c>
@@ -2538,7 +2519,7 @@
       <c r="E34" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="H34" s="56"/>
+      <c r="H34" s="48"/>
       <c r="I34" s="19" t="s">
         <v>127</v>
       </c>
@@ -2574,13 +2555,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.6328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.36328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
@@ -2593,49 +2574,49 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="9"/>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="70"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="62"/>
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
-      <c r="H1" s="57" t="s">
+      <c r="H1" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="9"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="73"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1">
       <c r="A3" s="9"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="68"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
     </row>
     <row r="4" spans="1:12" ht="28.5" thickBot="1">
       <c r="A4" s="9"/>
@@ -2671,7 +2652,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="9"/>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="58" t="s">
         <v>202</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -2685,14 +2666,14 @@
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="54" t="s">
+      <c r="H5" s="46" t="s">
         <v>202</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>95</v>
+        <v>208</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>96</v>
+        <v>209</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>71</v>
@@ -2703,7 +2684,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="9"/>
-      <c r="B6" s="67"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
@@ -2715,7 +2696,7 @@
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="55"/>
+      <c r="H6" s="47"/>
       <c r="I6" s="6" t="s">
         <v>98</v>
       </c>
@@ -2731,7 +2712,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="9"/>
-      <c r="B7" s="67"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
@@ -2743,23 +2724,23 @@
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="55"/>
+      <c r="H7" s="47"/>
       <c r="I7" s="6" t="s">
-        <v>101</v>
+        <v>210</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>102</v>
+        <v>211</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>68</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="9"/>
-      <c r="B8" s="67"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
@@ -2771,12 +2752,12 @@
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="55"/>
+      <c r="H8" s="47"/>
       <c r="I8" s="6" t="s">
-        <v>104</v>
+        <v>213</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>105</v>
+        <v>214</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>57</v>
@@ -2787,7 +2768,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="9"/>
-      <c r="B9" s="67"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="30" t="s">
         <v>15</v>
       </c>
@@ -2799,23 +2780,23 @@
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="55"/>
+      <c r="H9" s="47"/>
       <c r="I9" s="6" t="s">
-        <v>106</v>
+        <v>215</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>89</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" thickBot="1">
       <c r="A10" s="9"/>
-      <c r="B10" s="68"/>
+      <c r="B10" s="60"/>
       <c r="C10" s="15" t="s">
         <v>18</v>
       </c>
@@ -2827,7 +2808,7 @@
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="56"/>
+      <c r="H10" s="48"/>
       <c r="I10" s="19" t="s">
         <v>109</v>
       </c>
@@ -2843,7 +2824,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="9"/>
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="58" t="s">
         <v>203</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -2857,7 +2838,7 @@
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="77" t="s">
+      <c r="H11" s="69" t="s">
         <v>203</v>
       </c>
       <c r="I11" s="14" t="s">
@@ -2875,7 +2856,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="9"/>
-      <c r="B12" s="67"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="5" t="s">
         <v>150</v>
       </c>
@@ -2887,7 +2868,7 @@
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="78"/>
+      <c r="H12" s="70"/>
       <c r="I12" s="5" t="s">
         <v>133</v>
       </c>
@@ -2903,7 +2884,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="9"/>
-      <c r="B13" s="67"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="5" t="s">
         <v>151</v>
       </c>
@@ -2915,7 +2896,7 @@
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="78"/>
+      <c r="H13" s="70"/>
       <c r="I13" s="5" t="s">
         <v>193</v>
       </c>
@@ -2931,7 +2912,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="9"/>
-      <c r="B14" s="67"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="28" t="s">
         <v>152</v>
       </c>
@@ -2943,11 +2924,11 @@
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="50" t="s">
+      <c r="H14" s="70"/>
+      <c r="I14" s="42" t="s">
         <v>194</v>
       </c>
-      <c r="J14" s="51" t="s">
+      <c r="J14" s="43" t="s">
         <v>196</v>
       </c>
       <c r="K14" s="6" t="s">
@@ -2957,7 +2938,7 @@
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1">
       <c r="A15" s="9"/>
-      <c r="B15" s="67"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="8" t="s">
         <v>153</v>
       </c>
@@ -2969,11 +2950,11 @@
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="52" t="s">
+      <c r="H15" s="70"/>
+      <c r="I15" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="J15" s="53" t="s">
+      <c r="J15" s="45" t="s">
         <v>143</v>
       </c>
       <c r="K15" s="6" t="s">
@@ -2985,7 +2966,7 @@
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1">
       <c r="A16" s="9"/>
-      <c r="B16" s="68"/>
+      <c r="B16" s="60"/>
       <c r="C16" s="32" t="s">
         <v>142</v>
       </c>
@@ -2997,11 +2978,11 @@
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="52" t="s">
+      <c r="H16" s="71"/>
+      <c r="I16" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="53" t="s">
+      <c r="J16" s="45" t="s">
         <v>146</v>
       </c>
       <c r="K16" s="19" t="s">
@@ -3011,9 +2992,9 @@
         <v>147</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15" thickBot="1">
+    <row r="17" spans="1:12" ht="15" thickBot="1">
       <c r="A17" s="9"/>
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="58" t="s">
         <v>204</v>
       </c>
       <c r="C17" s="14" t="s">
@@ -3027,7 +3008,7 @@
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="77" t="s">
+      <c r="H17" s="69" t="s">
         <v>204</v>
       </c>
       <c r="I17" s="16" t="s">
@@ -3043,9 +3024,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15" thickBot="1">
+    <row r="18" spans="1:12" ht="15" thickBot="1">
       <c r="A18" s="9"/>
-      <c r="B18" s="67"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
@@ -3057,7 +3038,7 @@
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="78"/>
+      <c r="H18" s="70"/>
       <c r="I18" s="6" t="s">
         <v>59</v>
       </c>
@@ -3071,9 +3052,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15" thickBot="1">
+    <row r="19" spans="1:12" ht="15" thickBot="1">
       <c r="A19" s="9"/>
-      <c r="B19" s="67"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
@@ -3085,19 +3066,21 @@
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="78"/>
+      <c r="H19" s="70"/>
       <c r="I19" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="J19" s="6"/>
+      <c r="J19" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="K19" s="6" t="s">
         <v>89</v>
       </c>
       <c r="L19" s="18"/>
     </row>
-    <row r="20" spans="1:18" ht="15" thickBot="1">
+    <row r="20" spans="1:12" ht="15" thickBot="1">
       <c r="A20" s="9"/>
-      <c r="B20" s="67"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="28" t="s">
         <v>186</v>
       </c>
@@ -3109,7 +3092,7 @@
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-      <c r="H20" s="78"/>
+      <c r="H20" s="70"/>
       <c r="I20" s="6" t="s">
         <v>66</v>
       </c>
@@ -3123,9 +3106,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15" thickBot="1">
+    <row r="21" spans="1:12" ht="15" thickBot="1">
       <c r="A21" s="9"/>
-      <c r="B21" s="67"/>
+      <c r="B21" s="59"/>
       <c r="C21" s="28" t="s">
         <v>189</v>
       </c>
@@ -3137,7 +3120,7 @@
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
-      <c r="H21" s="78"/>
+      <c r="H21" s="70"/>
       <c r="I21" s="6" t="s">
         <v>69</v>
       </c>
@@ -3151,9 +3134,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15" thickBot="1">
+    <row r="22" spans="1:12" ht="15" thickBot="1">
       <c r="A22" s="9"/>
-      <c r="B22" s="68"/>
+      <c r="B22" s="60"/>
       <c r="C22" s="28" t="s">
         <v>191</v>
       </c>
@@ -3165,7 +3148,7 @@
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
-      <c r="H22" s="79"/>
+      <c r="H22" s="71"/>
       <c r="I22" s="19" t="s">
         <v>72</v>
       </c>
@@ -3179,9 +3162,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:12">
       <c r="A23" s="9"/>
-      <c r="B23" s="66" t="s">
+      <c r="B23" s="58" t="s">
         <v>205</v>
       </c>
       <c r="C23" s="14" t="s">
@@ -3195,7 +3178,7 @@
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="54" t="s">
+      <c r="H23" s="46" t="s">
         <v>205</v>
       </c>
       <c r="I23" s="16" t="s">
@@ -3211,9 +3194,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:12">
       <c r="A24" s="9"/>
-      <c r="B24" s="67"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="5" t="s">
         <v>43</v>
       </c>
@@ -3225,7 +3208,7 @@
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="55"/>
+      <c r="H24" s="47"/>
       <c r="I24" s="6" t="s">
         <v>78</v>
       </c>
@@ -3239,9 +3222,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:12">
       <c r="A25" s="9"/>
-      <c r="B25" s="67"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="5" t="s">
         <v>45</v>
       </c>
@@ -3253,7 +3236,7 @@
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="55"/>
+      <c r="H25" s="47"/>
       <c r="I25" s="6" t="s">
         <v>81</v>
       </c>
@@ -3267,9 +3250,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:12">
       <c r="A26" s="9"/>
-      <c r="B26" s="67"/>
+      <c r="B26" s="59"/>
       <c r="C26" s="5" t="s">
         <v>46</v>
       </c>
@@ -3281,7 +3264,7 @@
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
-      <c r="H26" s="55"/>
+      <c r="H26" s="47"/>
       <c r="I26" s="6" t="s">
         <v>84</v>
       </c>
@@ -3295,9 +3278,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:12">
       <c r="A27" s="9"/>
-      <c r="B27" s="67"/>
+      <c r="B27" s="59"/>
       <c r="C27" s="8" t="s">
         <v>47</v>
       </c>
@@ -3309,7 +3292,7 @@
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="H27" s="55"/>
+      <c r="H27" s="47"/>
       <c r="I27" s="6" t="s">
         <v>87</v>
       </c>
@@ -3323,9 +3306,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15" thickBot="1">
+    <row r="28" spans="1:12" ht="15" thickBot="1">
       <c r="A28" s="9"/>
-      <c r="B28" s="68"/>
+      <c r="B28" s="60"/>
       <c r="C28" s="15" t="s">
         <v>48</v>
       </c>
@@ -3337,7 +3320,7 @@
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="56"/>
+      <c r="H28" s="48"/>
       <c r="I28" s="19" t="s">
         <v>91</v>
       </c>
@@ -3351,9 +3334,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15" thickBot="1">
+    <row r="29" spans="1:12">
       <c r="A29" s="9"/>
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="58" t="s">
         <v>206</v>
       </c>
       <c r="C29" s="26" t="s">
@@ -3367,7 +3350,7 @@
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="54" t="s">
+      <c r="H29" s="46" t="s">
         <v>206</v>
       </c>
       <c r="I29" s="16" t="s">
@@ -3380,22 +3363,10 @@
         <v>61</v>
       </c>
       <c r="L29" s="17"/>
-      <c r="O29" s="80" t="s">
-        <v>167</v>
-      </c>
-      <c r="P29" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q29" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="R29" s="44" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="15" thickBot="1">
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="9"/>
-      <c r="B30" s="67"/>
+      <c r="B30" s="59"/>
       <c r="C30" s="28" t="s">
         <v>171</v>
       </c>
@@ -3407,7 +3378,7 @@
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="55"/>
+      <c r="H30" s="47"/>
       <c r="I30" s="6" t="s">
         <v>116</v>
       </c>
@@ -3420,18 +3391,10 @@
       <c r="L30" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="O30" s="81"/>
-      <c r="P30" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q30" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="R30" s="47"/>
-    </row>
-    <row r="31" spans="1:18" ht="15" thickBot="1">
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="9"/>
-      <c r="B31" s="67"/>
+      <c r="B31" s="59"/>
       <c r="C31" s="28" t="s">
         <v>172</v>
       </c>
@@ -3443,7 +3406,7 @@
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="55"/>
+      <c r="H31" s="47"/>
       <c r="I31" s="6" t="s">
         <v>119</v>
       </c>
@@ -3456,18 +3419,10 @@
       <c r="L31" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="O31" s="81"/>
-      <c r="P31" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q31" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="R31" s="47"/>
-    </row>
-    <row r="32" spans="1:18" ht="15" thickBot="1">
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="9"/>
-      <c r="B32" s="67"/>
+      <c r="B32" s="59"/>
       <c r="C32" s="28" t="s">
         <v>174</v>
       </c>
@@ -3479,7 +3434,7 @@
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="55"/>
+      <c r="H32" s="47"/>
       <c r="I32" s="6" t="s">
         <v>121</v>
       </c>
@@ -3492,18 +3447,10 @@
       <c r="L32" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="O32" s="81"/>
-      <c r="P32" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q32" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="R32" s="47"/>
-    </row>
-    <row r="33" spans="1:18" ht="15" thickBot="1">
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="9"/>
-      <c r="B33" s="67"/>
+      <c r="B33" s="59"/>
       <c r="C33" s="30" t="s">
         <v>177</v>
       </c>
@@ -3515,7 +3462,7 @@
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
-      <c r="H33" s="55"/>
+      <c r="H33" s="47"/>
       <c r="I33" s="6" t="s">
         <v>124</v>
       </c>
@@ -3528,18 +3475,10 @@
       <c r="L33" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="O33" s="81"/>
-      <c r="P33" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q33" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="R33" s="47"/>
-    </row>
-    <row r="34" spans="1:18" ht="15" thickBot="1">
+    </row>
+    <row r="34" spans="1:12" ht="15" thickBot="1">
       <c r="A34" s="9"/>
-      <c r="B34" s="68"/>
+      <c r="B34" s="60"/>
       <c r="C34" s="32" t="s">
         <v>127</v>
       </c>
@@ -3551,7 +3490,7 @@
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="56"/>
+      <c r="H34" s="48"/>
       <c r="I34" s="19" t="s">
         <v>200</v>
       </c>
@@ -3562,26 +3501,15 @@
         <v>64</v>
       </c>
       <c r="L34" s="20"/>
-      <c r="O34" s="82"/>
-      <c r="P34" s="48" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q34" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="R34" s="47" t="s">
-        <v>201</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="B1:E3"/>
     <mergeCell ref="H1:L3"/>
     <mergeCell ref="B5:B10"/>
     <mergeCell ref="H5:H10"/>
     <mergeCell ref="B11:B16"/>
     <mergeCell ref="H11:H16"/>
-    <mergeCell ref="O29:O34"/>
     <mergeCell ref="B17:B22"/>
     <mergeCell ref="H17:H22"/>
     <mergeCell ref="B23:B28"/>
@@ -3609,27 +3537,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1">
-      <c r="A3" s="61"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
     </row>
     <row r="4" spans="1:9" ht="28.5" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -3649,7 +3577,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="46" t="s">
         <v>94</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -3666,7 +3594,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1">
-      <c r="A6" s="55"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="6" t="s">
         <v>98</v>
       </c>
@@ -3681,7 +3609,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1">
-      <c r="A7" s="55"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="6" t="s">
         <v>101</v>
       </c>
@@ -3705,7 +3633,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1">
-      <c r="A8" s="55"/>
+      <c r="A8" s="47"/>
       <c r="B8" s="6" t="s">
         <v>104</v>
       </c>
@@ -3729,7 +3657,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" thickBot="1">
-      <c r="A9" s="55"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="6" t="s">
         <v>106</v>
       </c>
@@ -3753,7 +3681,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1">
-      <c r="A10" s="56"/>
+      <c r="A10" s="48"/>
       <c r="B10" s="19" t="s">
         <v>109</v>
       </c>
@@ -3777,7 +3705,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" thickBot="1">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="69" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -3803,7 +3731,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" thickBot="1">
-      <c r="A12" s="78"/>
+      <c r="A12" s="70"/>
       <c r="B12" s="5" t="s">
         <v>133</v>
       </c>
@@ -3819,13 +3747,13 @@
       <c r="G12" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="83" t="s">
+      <c r="H12" s="72" t="s">
         <v>188</v>
       </c>
-      <c r="I12" s="84"/>
+      <c r="I12" s="73"/>
     </row>
     <row r="13" spans="1:9" ht="15" thickBot="1">
-      <c r="A13" s="78"/>
+      <c r="A13" s="70"/>
       <c r="B13" s="5" t="s">
         <v>193</v>
       </c>
@@ -3849,7 +3777,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1">
-      <c r="A14" s="78"/>
+      <c r="A14" s="70"/>
       <c r="B14" s="28" t="s">
         <v>194</v>
       </c>
@@ -3871,7 +3799,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1">
-      <c r="A15" s="78"/>
+      <c r="A15" s="70"/>
       <c r="B15" s="32" t="s">
         <v>142</v>
       </c>
@@ -3886,7 +3814,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" thickBot="1">
-      <c r="A16" s="79"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="32" t="s">
         <v>145</v>
       </c>
@@ -3901,7 +3829,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="58" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="14" t="s">
@@ -3916,7 +3844,7 @@
       <c r="E17" s="14"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="67"/>
+      <c r="A18" s="59"/>
       <c r="B18" s="5" t="s">
         <v>33</v>
       </c>
@@ -3929,7 +3857,7 @@
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="67"/>
+      <c r="A19" s="59"/>
       <c r="B19" s="5" t="s">
         <v>35</v>
       </c>
@@ -3942,7 +3870,7 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="67"/>
+      <c r="A20" s="59"/>
       <c r="B20" s="28" t="s">
         <v>186</v>
       </c>
@@ -3955,7 +3883,7 @@
       <c r="E20" s="28"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="67"/>
+      <c r="A21" s="59"/>
       <c r="B21" s="28" t="s">
         <v>189</v>
       </c>
@@ -3968,7 +3896,7 @@
       <c r="E21" s="28"/>
     </row>
     <row r="22" spans="1:5" ht="15" thickBot="1">
-      <c r="A22" s="68"/>
+      <c r="A22" s="60"/>
       <c r="B22" s="28" t="s">
         <v>191</v>
       </c>
@@ -3981,7 +3909,7 @@
       <c r="E22" s="28"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="46" t="s">
         <v>40</v>
       </c>
       <c r="B23" s="16" t="s">
@@ -3998,7 +3926,7 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="55"/>
+      <c r="A24" s="47"/>
       <c r="B24" s="6" t="s">
         <v>78</v>
       </c>
@@ -4013,7 +3941,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="55"/>
+      <c r="A25" s="47"/>
       <c r="B25" s="6" t="s">
         <v>81</v>
       </c>
@@ -4028,7 +3956,7 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="55"/>
+      <c r="A26" s="47"/>
       <c r="B26" s="6" t="s">
         <v>84</v>
       </c>
@@ -4043,7 +3971,7 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="55"/>
+      <c r="A27" s="47"/>
       <c r="B27" s="6" t="s">
         <v>87</v>
       </c>
@@ -4058,7 +3986,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" thickBot="1">
-      <c r="A28" s="56"/>
+      <c r="A28" s="48"/>
       <c r="B28" s="19" t="s">
         <v>91</v>
       </c>
@@ -4073,7 +4001,7 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="46" t="s">
         <v>112</v>
       </c>
       <c r="B29" s="16" t="s">
@@ -4090,7 +4018,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="55"/>
+      <c r="A30" s="47"/>
       <c r="B30" s="6" t="s">
         <v>116</v>
       </c>
@@ -4105,7 +4033,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="55"/>
+      <c r="A31" s="47"/>
       <c r="B31" s="6" t="s">
         <v>119</v>
       </c>
@@ -4120,7 +4048,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="55"/>
+      <c r="A32" s="47"/>
       <c r="B32" s="6" t="s">
         <v>121</v>
       </c>
@@ -4135,7 +4063,7 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="55"/>
+      <c r="A33" s="47"/>
       <c r="B33" s="6" t="s">
         <v>124</v>
       </c>
@@ -4150,7 +4078,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" thickBot="1">
-      <c r="A34" s="56"/>
+      <c r="A34" s="48"/>
       <c r="B34" s="19" t="s">
         <v>127</v>
       </c>
